--- a/Results/Phase 2/Carbon dioxide/carbon dioxide resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide resource use mineral and metals results.xlsx
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.984319784501192e-06</v>
+        <v>2.984319784501193e-06</v>
       </c>
       <c r="C9" t="n">
         <v>2.543890664054243e-06</v>
@@ -2699,10 +2699,10 @@
         <v>3.080942553597701e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>3.31178321350624e-06</v>
+        <v>3.311783213506239e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.204661208058067e-06</v>
+        <v>3.204661208058066e-06</v>
       </c>
       <c r="K9" t="n">
         <v>2.858083521605571e-06</v>
@@ -2769,10 +2769,10 @@
         <v>6.316733252413949e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="E10" t="n">
         <v>7.739990774095438e-06</v>
@@ -2784,22 +2784,22 @@
         <v>9.992178860427651e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>9.360942286080881e-06</v>
+        <v>9.360942286080879e-06</v>
       </c>
       <c r="N10" t="n">
         <v>7.001171000050046e-06</v>
@@ -2814,13 +2814,13 @@
         <v>5.718476696477795e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="U10" t="n">
         <v>7.875232869805551e-06</v>
@@ -2841,7 +2841,7 @@
         <v>6.260185506670443e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.360942286080921e-06</v>
+        <v>9.360942286080919e-06</v>
       </c>
       <c r="AB10" t="n">
         <v>1.254087317486034e-05</v>
@@ -2905,7 +2905,7 @@
         <v>1.945141118998794e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>1.935528258951285e-06</v>
+        <v>1.935528258951286e-06</v>
       </c>
       <c r="T11" t="n">
         <v>1.945141118998794e-06</v>
@@ -3215,7 +3215,7 @@
         <v>2.466972766252027e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>1.848992386278719e-06</v>
+        <v>1.848992386278718e-06</v>
       </c>
       <c r="F15" t="n">
         <v>2.089715679131287e-06</v>
@@ -3230,7 +3230,7 @@
         <v>2.409877779661524e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>2.351152641549688e-06</v>
+        <v>2.351152641549689e-06</v>
       </c>
       <c r="K15" t="n">
         <v>2.186872841848608e-06</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.430840299662822e-06</v>
+        <v>1.430840299662527e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.335139004357073e-06</v>
+        <v>1.335139004357074e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.628704066680582e-06</v>
+        <v>1.628704066680302e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>8.576379458296106e-07</v>
+        <v>8.576379458296071e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.217502915948914e-06</v>
+        <v>1.217502915948908e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.578253818545793e-06</v>
+        <v>1.57825381854534e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.318474574501045e-06</v>
+        <v>1.318474574500777e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.545466349861386e-06</v>
+        <v>1.545466349861101e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.462609191066112e-06</v>
+        <v>1.462609191065361e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.616021544349782e-06</v>
+        <v>1.616021544349494e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.373854457200002e-06</v>
+        <v>1.373854457199711e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.503616170488118e-06</v>
+        <v>1.503616170488098e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.378567155358765e-06</v>
+        <v>1.378567155358516e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.240928789078524e-06</v>
+        <v>1.240928789078239e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.246417514328952e-06</v>
+        <v>1.246417514328715e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.350408654456557e-06</v>
+        <v>1.350408654456273e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.380184186322042e-06</v>
+        <v>1.380184186321763e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.444093454373699e-06</v>
+        <v>1.444093454373411e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.457590499601944e-06</v>
+        <v>1.457590499601573e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.404682449099222e-06</v>
+        <v>1.40468244909856e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.370542798981971e-06</v>
+        <v>1.37054279898203e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.752163059462405e-06</v>
+        <v>1.752163059462132e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.407116944712112e-06</v>
+        <v>1.407116944711832e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.343800681261184e-06</v>
+        <v>1.343800681260879e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.481724593932024e-06</v>
+        <v>1.481724593931736e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.488794300090764e-06</v>
+        <v>1.48879430009047e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.568507568759415e-06</v>
+        <v>1.568507568759418e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.858646686480483e-06</v>
+        <v>4.85864668648019e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.762267957161145e-06</v>
+        <v>7.762267957161144e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.162349885233865e-06</v>
+        <v>6.162349885233871e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.290365445287495e-06</v>
+        <v>5.290365445287486e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.272947702976496e-06</v>
+        <v>8.272947702976602e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.67733724603273e-06</v>
+        <v>7.677337246032623e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.672164956042936e-06</v>
+        <v>7.672164956042941e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.494454353555397e-06</v>
+        <v>5.494454353555305e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.096864350428564e-06</v>
+        <v>6.096864350428551e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.949199103899898e-06</v>
+        <v>5.94919910389997e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.302896939398703e-06</v>
+        <v>4.302896939398375e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.306329972899508e-06</v>
+        <v>6.306329972899396e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.89085035752872e-06</v>
+        <v>6.890850357528747e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.687116972051107e-06</v>
+        <v>7.687116972050851e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.562080924511627e-06</v>
+        <v>4.562080924511378e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.049835400092014e-05</v>
+        <v>1.049835400092002e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.806116722398173e-06</v>
+        <v>4.806116722398117e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.686561205311003e-06</v>
+        <v>7.68656120531099e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.062228481808462e-05</v>
+        <v>1.062228481808461e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.046900442433394e-06</v>
+        <v>1.04690044243319e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.060130973870079e-06</v>
+        <v>1.060130973870051e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.119019462077764e-06</v>
+        <v>1.119019462077475e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.262622706267915e-07</v>
+        <v>8.262622706267851e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.6352528059718e-07</v>
+        <v>9.635252805971631e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.10063093904927e-06</v>
+        <v>1.100630939049021e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.005944455076898e-06</v>
+        <v>1.005944455076681e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.088680291723739e-06</v>
+        <v>1.088680291723513e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.060818941320447e-06</v>
+        <v>1.060818941320142e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.114396831613812e-06</v>
+        <v>1.114396831613613e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.026129772017275e-06</v>
+        <v>1.026129772017016e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.064277407312677e-06</v>
+        <v>1.064277407312583e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.027847495156814e-06</v>
+        <v>1.027847495156604e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.776799268789909e-07</v>
+        <v>9.776799268787694e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.796805027809181e-07</v>
+        <v>9.796805027806005e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.017584052231782e-06</v>
+        <v>1.017584052231551e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.028436883954816e-06</v>
+        <v>1.028436883954576e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.051731061699139e-06</v>
+        <v>1.051731061698851e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.05665057619454e-06</v>
+        <v>1.056650576194249e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.037366213064017e-06</v>
+        <v>1.037366213063752e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.065123606338991e-06</v>
+        <v>1.065123606339062e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.164018815217988e-06</v>
+        <v>1.164018815217759e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.038253558127586e-06</v>
+        <v>1.038253558127375e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.015175523596781e-06</v>
+        <v>1.015175523596568e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.06544717018099e-06</v>
+        <v>1.065447170180739e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.068023995059183e-06</v>
+        <v>1.068023995058923e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08546801982945e-06</v>
+        <v>1.085468019829341e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.296295619093671e-06</v>
+        <v>2.296295619093399e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.402744006008637e-06</v>
+        <v>3.402744006008594e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.759767481467133e-06</v>
+        <v>2.759767481467123e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.448035846574697e-06</v>
+        <v>2.448035846574602e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.540768246859599e-06</v>
+        <v>3.540768246859635e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.326014340334215e-06</v>
+        <v>3.3260143403344e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3126410048905e-06</v>
+        <v>3.312641004890433e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52804004771193e-06</v>
+        <v>2.52804004771174e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.747611417716928e-06</v>
+        <v>2.747611417716694e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.693789169330181e-06</v>
+        <v>2.693789169329876e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.093731362225123e-06</v>
+        <v>2.093731362225081e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.823959177437876e-06</v>
+        <v>2.823959177437837e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.077210888705195e-06</v>
+        <v>3.077210888705919e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.327239824609098e-06</v>
+        <v>3.327239824608948e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.18820088130717e-06</v>
+        <v>2.188200881306771e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.351902710419777e-06</v>
+        <v>4.351902710419874e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.277149064023785e-06</v>
+        <v>2.277149064023485e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.327037254158496e-06</v>
+        <v>3.327037254158417e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.385463512388338e-06</v>
+        <v>4.385463512388347e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.875759377633099e-07</v>
+        <v>7.875759377630844e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.008064691999255e-07</v>
+        <v>8.008064691999257e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>8.596949574076498e-07</v>
+        <v>8.596949574074099e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.669377659566927e-07</v>
+        <v>5.669377659566896e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.042007759270497e-07</v>
+        <v>7.042007759270478e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.345186854845871e-07</v>
+        <v>8.345186854841508e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.466199504067917e-07</v>
+        <v>7.466199504065894e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>8.293557870536519e-07</v>
+        <v>8.293557870534276e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.867589514593056e-07</v>
+        <v>7.867589514591775e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.55072326943727e-07</v>
+        <v>8.550723269435263e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.668052673471651e-07</v>
+        <v>7.668052673469333e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>8.049529026425045e-07</v>
+        <v>8.049529026424971e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.685229904867067e-07</v>
+        <v>7.685229904865189e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.1156767331408e-07</v>
+        <v>7.115676733138786e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.135682492159812e-07</v>
+        <v>7.13568249215777e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.582595475616804e-07</v>
+        <v>7.582595475614679e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.691123792846925e-07</v>
+        <v>7.69112379284493e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.924065570290347e-07</v>
+        <v>7.92406557028802e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>7.973260715243821e-07</v>
+        <v>7.973260715241772e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.71253959499089e-07</v>
+        <v>7.712539594989105e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.446684201122272e-07</v>
+        <v>7.446684201123152e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.979065616531099e-07</v>
+        <v>8.979065616529226e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.721413045626861e-07</v>
+        <v>7.721413045624704e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.558510189267038e-07</v>
+        <v>7.558510189264838e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.061226655108859e-07</v>
+        <v>8.061226655106615e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.086994903890508e-07</v>
+        <v>8.086994903888404e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.261435151592529e-07</v>
+        <v>8.261435151592549e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5454,82 +5454,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036971114423534e-06</v>
+        <v>2.036971114423326e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.143419501338464e-06</v>
+        <v>3.143419501338466e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.500442976797007e-06</v>
+        <v>2.500442976797005e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.188711341904512e-06</v>
+        <v>2.18871134190451e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.274655993294658e-06</v>
+        <v>3.274655993294755e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.051954350473576e-06</v>
+        <v>3.051954350473363e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488315e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.053316500220324e-06</v>
+        <v>3.05331650022032e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.268715543041825e-06</v>
+        <v>2.268715543041634e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.481499164152038e-06</v>
+        <v>2.481499164151822e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.427676915765285e-06</v>
+        <v>2.427676915765025e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83440685755499e-06</v>
+        <v>1.834406857555018e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488315e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488315e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.557846923872971e-06</v>
+        <v>2.557846923872925e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.756755702478403e-06</v>
+        <v>2.75675570247851e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.061127571044151e-06</v>
+        <v>3.061127571044072e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.92208862774227e-06</v>
+        <v>1.922088627741912e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.092578205749624e-06</v>
+        <v>4.092578205749814e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.017824559353633e-06</v>
+        <v>2.017824559353387e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.067712749488335e-06</v>
+        <v>3.067712749488316e-06</v>
       </c>
       <c r="AB7" t="n">
         <v>4.126139007718219e-06</v>
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="P8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.763940716541634e-06</v>
+        <v>1.763940716541635e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.765116833806318e-06</v>
+        <v>1.765116833806329e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.612565542367871e-06</v>
+        <v>2.612565542367875e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>2.428352801606033e-06</v>
+        <v>2.428352801606037e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>2.82521032436413e-06</v>
+        <v>2.82521032436411e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>2.016350311173697e-06</v>
+        <v>2.016350311173695e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.392788661693643e-06</v>
+        <v>2.392788661693633e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.77099129185496e-06</v>
+        <v>2.770991291854989e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>2.49180576158028e-06</v>
+        <v>2.491805761580299e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>2.735754501230543e-06</v>
+        <v>2.735754501230548e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>2.656620681557748e-06</v>
+        <v>2.656620681557774e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>2.811580379696406e-06</v>
+        <v>2.81158037969641e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.55132268709418e-06</v>
+        <v>2.551322687094178e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.706249680463658e-06</v>
+        <v>2.706249680463641e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>2.556387437895682e-06</v>
+        <v>2.55638743789567e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>2.408467074136715e-06</v>
+        <v>2.40846707413671e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>2.414365823573792e-06</v>
+        <v>2.41436582357373e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.526125412786463e-06</v>
+        <v>2.526125412786449e-06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.558125265906568e-06</v>
+        <v>2.55812526590656e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>2.626808747360544e-06</v>
+        <v>2.626808747360542e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>2.641314062221436e-06</v>
+        <v>2.641314062221354e-06</v>
       </c>
       <c r="U9" t="n">
-        <v>2.584453622159227e-06</v>
+        <v>2.584453622159307e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.572308766505439e-06</v>
+        <v>2.572308766505485e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>2.957892073030146e-06</v>
+        <v>2.957892073030066e-06</v>
       </c>
       <c r="X9" t="n">
-        <v>2.587069981873167e-06</v>
+        <v>2.587069981873178e-06</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.519023804236533e-06</v>
+        <v>2.519023804236538e-06</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.667251045555202e-06</v>
+        <v>2.667251045555205e-06</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.674848879901349e-06</v>
+        <v>2.674848879901336e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.78015132847636e-06</v>
+        <v>2.780151328476365e-06</v>
       </c>
     </row>
     <row r="10">
@@ -5718,70 +5718,70 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.296439314894973e-06</v>
+        <v>6.29643931489497e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>7.717340092724693e-06</v>
+        <v>7.717340092724679e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>6.769906199206663e-06</v>
+        <v>6.769906199206673e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>9.965798825558843e-06</v>
+        <v>9.965798825558832e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>9.335607503312015e-06</v>
+        <v>9.335607503312019e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>6.979743715667784e-06</v>
+        <v>6.979743715667782e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>7.627155540420745e-06</v>
+        <v>7.627155540420736e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>7.468459258480086e-06</v>
+        <v>7.468459258480091e-06</v>
       </c>
       <c r="Q10" t="n">
         <v>5.699173400099836e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>7.852268871160169e-06</v>
+        <v>7.852268871160174e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>8.504999804546623e-06</v>
+        <v>8.504999804546626e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>9.336204787489107e-06</v>
+        <v>9.336204787489104e-06</v>
       </c>
       <c r="X10" t="n">
         <v>5.977719203821046e-06</v>
@@ -5790,13 +5790,13 @@
         <v>1.235744962758135e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.239985205439443e-06</v>
+        <v>6.239985205439446e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.3356075033121e-06</v>
+        <v>9.335607503312114e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.251027280772833e-05</v>
+        <v>1.251027280772832e-05</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="C11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>1.872935430849904e-06</v>
+        <v>1.872935430849839e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="O11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>1.865305490682482e-06</v>
+        <v>1.865305490682429e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.912931803565615e-06</v>
+        <v>1.912931803565297e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.865883582231075e-06</v>
+        <v>1.865883582230928e-06</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.282426176211418e-06</v>
+        <v>2.282426176211415e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>2.191880928922753e-06</v>
+        <v>2.191880928922696e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>2.386946494897671e-06</v>
+        <v>2.386946494897615e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>1.98937122614396e-06</v>
+        <v>1.989371226143901e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>2.174400249629523e-06</v>
+        <v>2.174400249629519e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.360296461430949e-06</v>
+        <v>2.360296461430957e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>2.223069672591119e-06</v>
+        <v>2.223069672591032e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.342976682638535e-06</v>
+        <v>2.342976682638475e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>2.311132246225551e-06</v>
+        <v>2.311132246225334e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>2.380247030434119e-06</v>
+        <v>2.380247030434078e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>2.252323755214424e-06</v>
+        <v>2.252323755214393e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>2.328474312816015e-06</v>
+        <v>2.328474312815918e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.254813209048522e-06</v>
+        <v>2.254813209048473e-06</v>
       </c>
       <c r="O12" t="n">
-        <v>2.18210658810475e-06</v>
+        <v>2.182106588104695e-06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.185005973479884e-06</v>
+        <v>2.185005973479807e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.239938654033258e-06</v>
+        <v>2.239938654033231e-06</v>
       </c>
       <c r="R12" t="n">
-        <v>2.255667395715203e-06</v>
+        <v>2.255667395715147e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>2.289427073722185e-06</v>
+        <v>2.28942707372214e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.29655680489955e-06</v>
+        <v>2.296556804899401e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>2.268608452439837e-06</v>
+        <v>2.268608452440065e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.309687168332404e-06</v>
+        <v>2.309687168332638e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>2.452162948949533e-06</v>
+        <v>2.452162948949444e-06</v>
       </c>
       <c r="X12" t="n">
-        <v>2.269894459782846e-06</v>
+        <v>2.269894459782809e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.236448032811084e-06</v>
+        <v>2.236448032811047e-06</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.30930549188049e-06</v>
+        <v>2.30930549188045e-06</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.313040020702351e-06</v>
+        <v>2.313040020702307e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.364798852403645e-06</v>
+        <v>2.364798852403614e-06</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.093143829801754e-06</v>
+        <v>4.09314382980167e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>4.791552700812437e-06</v>
+        <v>4.791552700812374e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>4.325864845436722e-06</v>
+        <v>4.325864845436711e-06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.896727354535465e-06</v>
+        <v>5.896727354535439e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>5.594024140198189e-06</v>
+        <v>5.594024140198191e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>5.586972291579312e-06</v>
+        <v>5.58697229157923e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.429005321713403e-06</v>
+        <v>4.429005321713373e-06</v>
       </c>
       <c r="O13" t="n">
-        <v>4.747224699631771e-06</v>
+        <v>4.747224699631752e-06</v>
       </c>
       <c r="P13" t="n">
-        <v>4.669221440830675e-06</v>
+        <v>4.6692214408306e-06</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.799572442021673e-06</v>
+        <v>3.799572442021677e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>4.85787362714611e-06</v>
+        <v>4.857873627146129e-06</v>
       </c>
       <c r="V13" t="n">
-        <v>5.225755703576693e-06</v>
+        <v>5.225755703576434e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>5.587265871943514e-06</v>
+        <v>5.587265871943432e-06</v>
       </c>
       <c r="X13" t="n">
-        <v>3.936484788989953e-06</v>
+        <v>3.936484788989917e-06</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.072284552163039e-06</v>
+        <v>7.072284552163032e-06</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.065395199169685e-06</v>
+        <v>4.06539519916966e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.586972291579352e-06</v>
+        <v>5.586972291579272e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.147401032058125e-06</v>
+        <v>7.147401032058097e-06</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.637278761022585e-06</v>
+        <v>1.637278761022586e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>1.642319455146562e-06</v>
+        <v>1.642319455146565e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.637381170067548e-06</v>
+        <v>1.637381170067545e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.637060947418919e-06</v>
+        <v>1.637060947418922e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.642897546695127e-06</v>
+        <v>1.642897546695129e-06</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.059440140675505e-06</v>
+        <v>2.059440140675502e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>1.968894893386829e-06</v>
+        <v>1.968894893386834e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>2.163960459361765e-06</v>
+        <v>2.163960459361766e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>1.766385190608048e-06</v>
+        <v>1.766385190608053e-06</v>
       </c>
       <c r="F15" t="n">
-        <v>1.951414214093646e-06</v>
+        <v>1.951414214093644e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.131473826618995e-06</v>
+        <v>2.131473826618871e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>2.000083637055184e-06</v>
+        <v>2.000083637055191e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.119990647102607e-06</v>
+        <v>2.11999064710261e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>2.075475576398336e-06</v>
+        <v>2.075475576398206e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>2.157260994898203e-06</v>
+        <v>2.157260994898202e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.029337719678525e-06</v>
+        <v>2.02933771967852e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>2.105488277280106e-06</v>
+        <v>2.105488277280097e-06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.031827173512617e-06</v>
+        <v>2.031827173512602e-06</v>
       </c>
       <c r="O15" t="n">
         <v>1.953283953292622e-06</v>
       </c>
       <c r="P15" t="n">
-        <v>1.956183338667733e-06</v>
+        <v>1.956183338667731e-06</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.016952618497366e-06</v>
+        <v>2.016952618497367e-06</v>
       </c>
       <c r="R15" t="n">
-        <v>2.032681360179287e-06</v>
+        <v>2.032681360179286e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>2.066441038186237e-06</v>
+        <v>2.066441038186238e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>2.073570769363615e-06</v>
+        <v>2.073570769363581e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.039785817627727e-06</v>
+        <v>2.039785817627589e-06</v>
       </c>
       <c r="V15" t="n">
-        <v>2.034136534834382e-06</v>
+        <v>2.034136534834353e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>2.223340314137396e-06</v>
+        <v>2.223340314137389e-06</v>
       </c>
       <c r="X15" t="n">
-        <v>2.041071824970731e-06</v>
+        <v>2.041071824970741e-06</v>
       </c>
       <c r="Y15" t="n">
         <v>2.013461997275186e-06</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.086319456344573e-06</v>
+        <v>2.086319456344576e-06</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.090053985166444e-06</v>
+        <v>2.090053985166439e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.141812816867744e-06</v>
+        <v>2.141812816867746e-06</v>
       </c>
     </row>
     <row r="16">
@@ -6246,61 +6246,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.870157794265833e-06</v>
+        <v>3.870157794265836e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="E16" t="n">
         <v>4.568566665276512e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>4.102878809900824e-06</v>
+        <v>4.102878809900828e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>5.667904719723382e-06</v>
+        <v>5.667904719723377e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.358367470370918e-06</v>
+        <v>5.358367470370913e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>5.363986256043407e-06</v>
+        <v>5.363986256043412e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.206019286177519e-06</v>
+        <v>4.206019286177521e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>4.518402064819669e-06</v>
+        <v>4.51840206481967e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>4.44039880601855e-06</v>
+        <v>4.440398806018551e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.576586406485782e-06</v>
+        <v>3.576586406485781e-06</v>
       </c>
       <c r="R16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="U16" t="n">
         <v>4.62905099233403e-06</v>
@@ -6309,22 +6309,22 @@
         <v>4.950205070078769e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>5.358443237131358e-06</v>
+        <v>5.358443237131359e-06</v>
       </c>
       <c r="X16" t="n">
-        <v>3.70766215417783e-06</v>
+        <v>3.707662154177834e-06</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.849298516627149e-06</v>
+        <v>6.849298516627141e-06</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.842409163633814e-06</v>
+        <v>3.842409163633817e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.363986256043453e-06</v>
+        <v>5.363986256043452e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.924414996522196e-06</v>
+        <v>6.924414996522197e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.456309916284745e-06</v>
+        <v>1.456309916284714e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.34710455463373e-06</v>
+        <v>1.347104554633724e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.872548958540753e-06</v>
+        <v>1.872548958540569e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.001503409806746e-07</v>
+        <v>9.001503409806717e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.257758666336317e-06</v>
+        <v>1.257758666336273e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.661473280281143e-06</v>
+        <v>1.661473280280838e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.427856819058367e-06</v>
+        <v>1.427856819058333e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.660451075321726e-06</v>
+        <v>1.660451075321615e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.527666427330606e-06</v>
+        <v>1.527666427330525e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.581233336305999e-06</v>
+        <v>1.581233336305984e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.366061130196569e-06</v>
+        <v>1.366061130196334e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.568642553105784e-06</v>
+        <v>1.568642553105759e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.37148266814956e-06</v>
+        <v>1.371482668149442e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.350486879707902e-06</v>
+        <v>1.350486879707763e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.301956154863606e-06</v>
+        <v>1.301956154863551e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.338434392536213e-06</v>
+        <v>1.338434392536125e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.409945933753437e-06</v>
+        <v>1.409945933753287e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.432312052176717e-06</v>
+        <v>1.432312052176678e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.556679791593928e-06</v>
+        <v>1.556679791593811e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.440712936411246e-06</v>
+        <v>1.440712936411113e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.463192113995144e-06</v>
+        <v>1.463192113994989e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.949497175580176e-06</v>
+        <v>1.949497175580215e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.413344761698941e-06</v>
+        <v>1.413344761698811e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.433620257521386e-06</v>
+        <v>1.433620257521196e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.527236725527032e-06</v>
+        <v>1.527236725526935e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.651176549427787e-06</v>
+        <v>1.651176549427726e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.662472527288489e-06</v>
+        <v>1.662472527288476e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.866148663594973e-06</v>
+        <v>4.866148663594731e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.771234886212452e-06</v>
+        <v>7.771234886212438e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.170319726298548e-06</v>
+        <v>6.170319726298525e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.297937747100534e-06</v>
+        <v>5.297937747100524e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.282378002458812e-06</v>
+        <v>8.282378002458876e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.686343290856044e-06</v>
+        <v>7.686343290856066e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.681140574475447e-06</v>
+        <v>7.681140574475434e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.502315420901389e-06</v>
+        <v>5.502315420901183e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.105065645733758e-06</v>
+        <v>6.105065645733769e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.957317001111508e-06</v>
+        <v>5.95731700111156e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.310085041239287e-06</v>
+        <v>4.310085041239387e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.314718870430432e-06</v>
+        <v>6.314718870430545e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.899380347043172e-06</v>
+        <v>6.899380347043005e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.696216407175066e-06</v>
+        <v>7.696216407175044e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.569415407783358e-06</v>
+        <v>4.569415407783316e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.050915971431632e-05</v>
+        <v>1.050915971431633e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.813589031740609e-06</v>
+        <v>4.813589031740664e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.695660326553928e-06</v>
+        <v>7.695660326553931e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.063306492286092e-05</v>
+        <v>1.06330649228609e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.070676155725141e-06</v>
+        <v>1.070676155725216e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.078900603861727e-06</v>
+        <v>1.078900603861768e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.22239039890185e-06</v>
+        <v>1.222390398901653e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.560726653602323e-07</v>
+        <v>8.560726653602812e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.925769324540306e-07</v>
+        <v>9.925769324540255e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.145455792751947e-06</v>
+        <v>1.145455792751722e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.060305335899268e-06</v>
+        <v>1.060305335899278e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.145083211047612e-06</v>
+        <v>1.145083211047492e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.099331247914017e-06</v>
+        <v>1.099331247913997e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.116209275398023e-06</v>
+        <v>1.116209275398071e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.037781532950751e-06</v>
+        <v>1.037781532950558e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.102392609824614e-06</v>
+        <v>1.10239260982463e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.039757619871709e-06</v>
+        <v>1.039757619871521e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.032104901529718e-06</v>
+        <v>1.032104901529573e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.014416022200504e-06</v>
+        <v>1.014416022200335e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.027711911483087e-06</v>
+        <v>1.027711911482916e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.053777028525858e-06</v>
+        <v>1.053777028525756e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.061929216054923e-06</v>
+        <v>1.061929216054762e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.10725979667275e-06</v>
+        <v>1.107259796672556e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.064991239710239e-06</v>
+        <v>1.064991239710087e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.115698009641986e-06</v>
+        <v>1.115698009641754e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.250437120441146e-06</v>
+        <v>1.25043712044145e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.055015861400935e-06</v>
+        <v>1.055015861400774e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.062406041541327e-06</v>
+        <v>1.062406041541145e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.096528144829312e-06</v>
+        <v>1.096528144829071e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.141702755266241e-06</v>
+        <v>1.141702755266418e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.134217509316972e-06</v>
+        <v>1.134217509316948e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3135223387716e-06</v>
+        <v>2.313522338771698e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.420420673775229e-06</v>
+        <v>3.420420673775237e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.776987520855217e-06</v>
+        <v>2.776987520855248e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.465174765214566e-06</v>
+        <v>2.465174765214584e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.558697817397227e-06</v>
+        <v>3.558697817397326e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.344096645834067e-06</v>
+        <v>3.344096645834057e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.330326362038237e-06</v>
+        <v>3.330326362038254e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.545397651562564e-06</v>
+        <v>2.545397651562377e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.765093030663489e-06</v>
+        <v>2.765093030663366e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.711240384650853e-06</v>
+        <v>2.711240384650775e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.110843678051677e-06</v>
+        <v>2.110843678051661e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.841509169192958e-06</v>
+        <v>2.841509169192924e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.097124785642681e-06</v>
+        <v>3.097124785642631e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.34504879897327e-06</v>
+        <v>3.345048798973339e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.205366551446073e-06</v>
+        <v>2.2053665514459e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.370333603178253e-06</v>
+        <v>4.370333603178265e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29436497014704e-06</v>
+        <v>2.294364970146766e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.344846114116696e-06</v>
+        <v>3.344846114116759e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.403893099488923e-06</v>
+        <v>4.403893099488863e-06</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.004291281550414e-07</v>
+        <v>8.004291281549785e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.086535762916213e-07</v>
+        <v>8.086535762916184e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>9.52143371331748e-07</v>
+        <v>9.521433713315632e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.85825637790135e-07</v>
+        <v>5.858256377901323e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.223299048839209e-07</v>
+        <v>7.223299048839005e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.680213425443031e-07</v>
+        <v>8.680213425440879e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.900583083291622e-07</v>
+        <v>7.900583083291258e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>8.748361834775035e-07</v>
+        <v>8.748361834773298e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.135956888966518e-07</v>
+        <v>8.13595688896742e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.459622478279241e-07</v>
+        <v>8.459622478279491e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.675345053806334e-07</v>
+        <v>7.675345053804337e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>8.321455822545096e-07</v>
+        <v>8.321455822544821e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.695105923016094e-07</v>
+        <v>7.695105923014597e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.546704513220722e-07</v>
+        <v>7.546704513219095e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.369815719928652e-07</v>
+        <v>7.369815719926399e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.574648839129843e-07</v>
+        <v>7.574648839127895e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.835300009557481e-07</v>
+        <v>7.83530000955611e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.916821884848139e-07</v>
+        <v>7.916821884846652e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>8.370127691026575e-07</v>
+        <v>8.370127691024908e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.875567895025929e-07</v>
+        <v>7.87556789502418e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.814927843274989e-07</v>
+        <v>7.814927843273628e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>9.730026702334884e-07</v>
+        <v>9.730026702337959e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.775814111932905e-07</v>
+        <v>7.775814111930778e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.921590139712247e-07</v>
+        <v>7.921590139709976e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.262811172592113e-07</v>
+        <v>8.262811172590484e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.714557276961445e-07</v>
+        <v>8.714557276962216e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.639704817468672e-07</v>
+        <v>8.639704817468623e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.0432753112015e-06</v>
+        <v>2.043275311201598e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.150173646205114e-06</v>
+        <v>3.150173646205111e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.506740493285113e-06</v>
+        <v>2.506740493285106e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.194927737644459e-06</v>
+        <v>2.194927737644453e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.281263367189582e-06</v>
+        <v>3.281263367189675e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.058361086816724e-06</v>
+        <v>3.058361086816801e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.06007933446814e-06</v>
+        <v>3.060079334468131e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.275150623992462e-06</v>
+        <v>2.275150623992273e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.487658580455832e-06</v>
+        <v>2.487658580455702e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.433805934443205e-06</v>
+        <v>2.433805934443154e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84059665048157e-06</v>
+        <v>1.840596650481491e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.564074718985306e-06</v>
+        <v>2.564074718985252e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.762919560328382e-06</v>
+        <v>2.762919560328368e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.067614348765622e-06</v>
+        <v>3.067614348765709e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.927932101238425e-06</v>
+        <v>1.927932101238267e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.10008657560816e-06</v>
+        <v>4.100086575608165e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.024117942576939e-06</v>
+        <v>2.024117942576697e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.07459908654659e-06</v>
+        <v>3.074599086546667e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.133646071918819e-06</v>
+        <v>4.13364607191881e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469859e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="P8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.768684498719797e-06</v>
+        <v>1.768684498719794e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.774648472469864e-06</v>
+        <v>1.774648472469857e-06</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.63841881569054e-06</v>
+        <v>2.638418815690534e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>2.439835281795625e-06</v>
+        <v>2.439835281795609e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.085752158893826e-06</v>
+        <v>3.085752158893801e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>2.060819188362375e-06</v>
+        <v>2.060819188362367e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.43472446273493e-06</v>
+        <v>2.434724462734853e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.858908496384327e-06</v>
+        <v>2.858908496384149e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>2.607840187030968e-06</v>
+        <v>2.607840187030952e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>2.857809929658267e-06</v>
+        <v>2.857809929658246e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>2.725118917577537e-06</v>
+        <v>2.725118917577484e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>2.772674388689207e-06</v>
+        <v>2.772674388689173e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.541428175451536e-06</v>
+        <v>2.541428175451477e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.774747457309949e-06</v>
+        <v>2.774747457309907e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>2.547254718499239e-06</v>
+        <v>2.547254718499229e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>2.524690481886799e-06</v>
+        <v>2.524690481886784e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>2.472534366797222e-06</v>
+        <v>2.472534366797287e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.511737637888301e-06</v>
+        <v>2.511737637888289e-06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.588591305042966e-06</v>
+        <v>2.588591305042955e-06</v>
       </c>
       <c r="S9" t="n">
-        <v>2.612628239383718e-06</v>
+        <v>2.612628239383713e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>2.746286620775819e-06</v>
+        <v>2.746286620775812e-06</v>
       </c>
       <c r="U9" t="n">
-        <v>2.621656694787921e-06</v>
+        <v>2.621656694787886e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.67058494770487e-06</v>
+        <v>2.670584947704822e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>3.168448637809451e-06</v>
+        <v>3.168448637809432e-06</v>
       </c>
       <c r="X9" t="n">
-        <v>2.592244035597975e-06</v>
+        <v>2.592244035597946e-06</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.614034171578974e-06</v>
+        <v>2.614034171578785e-06</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.714644069643487e-06</v>
+        <v>2.714644069643482e-06</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.847842568950649e-06</v>
+        <v>2.847842568950625e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.879603173875433e-06</v>
+        <v>2.879603173875419e-06</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.302982712318524e-06</v>
+        <v>6.30298271231851e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>7.724685983759794e-06</v>
+        <v>7.724685983759781e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>6.776717000346596e-06</v>
+        <v>6.776717000346588e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>9.974414596796042e-06</v>
+        <v>9.974414596796025e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>9.343867356305356e-06</v>
+        <v>9.343867356305345e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>6.986673028436526e-06</v>
+        <v>6.986673028436515e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>7.634450497194406e-06</v>
+        <v>7.634450497194387e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>7.475664587073133e-06</v>
+        <v>7.475664587073112e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.705379474828115e-06</v>
+        <v>5.705379474828105e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>7.859765444606831e-06</v>
+        <v>7.859765444606813e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>8.512872695128724e-06</v>
+        <v>8.512872695128701e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>9.344464977811556e-06</v>
+        <v>9.344464977811536e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>5.984082595110958e-06</v>
+        <v>5.98408259511094e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.236754356026432e-05</v>
+        <v>1.236754356026429e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.246496718819415e-06</v>
+        <v>6.246496718819403e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.343867356305411e-06</v>
+        <v>9.343867356305392e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.252032564208937e-05</v>
+        <v>1.252032564208936e-05</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="C11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>1.889624826438903e-06</v>
+        <v>1.889624826438864e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869022e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="O11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>1.879326371085173e-06</v>
+        <v>1.879326371085209e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.931408721054124e-06</v>
+        <v>1.931408721054265e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.882257815869017e-06</v>
+        <v>1.882257815869027e-06</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.306822908403274e-06</v>
+        <v>2.306822908403251e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>2.209214050787822e-06</v>
+        <v>2.209214050787834e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>2.526698623911869e-06</v>
+        <v>2.526698623911922e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>2.022918001098895e-06</v>
+        <v>2.022918001098931e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>2.206701953232648e-06</v>
+        <v>2.206701953232636e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.41519919432386e-06</v>
+        <v>2.415199194323751e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>2.291792734690645e-06</v>
+        <v>2.291792734690664e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.414659220837412e-06</v>
+        <v>2.414659220837372e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>2.356805224151488e-06</v>
+        <v>2.356805224151482e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>2.372812937142708e-06</v>
+        <v>2.372812937142761e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>2.259149541898799e-06</v>
+        <v>2.259149541898811e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>2.373831903095525e-06</v>
+        <v>2.373831903095505e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.262013435997079e-06</v>
+        <v>2.262013435997091e-06</v>
       </c>
       <c r="O12" t="n">
-        <v>2.250922539810951e-06</v>
+        <v>2.250922539810923e-06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.225286482723507e-06</v>
+        <v>2.225286482723538e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24455588754745e-06</v>
+        <v>2.244555887547444e-06</v>
       </c>
       <c r="R12" t="n">
-        <v>2.282331419624008e-06</v>
+        <v>2.282331419624001e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>2.294146184199712e-06</v>
+        <v>2.29414618419973e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.359842678075757e-06</v>
+        <v>2.359842678075769e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>2.298583899657538e-06</v>
+        <v>2.298583899657529e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.371784285576752e-06</v>
+        <v>2.371784285576076e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>2.567346046573042e-06</v>
+        <v>2.567346046573004e-06</v>
       </c>
       <c r="X12" t="n">
-        <v>2.284126829594106e-06</v>
+        <v>2.284126829594029e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.294837235631682e-06</v>
+        <v>2.294837235631602e-06</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.344289559408335e-06</v>
+        <v>2.344289559408336e-06</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.409760009543159e-06</v>
+        <v>2.409760009543228e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.425371154652119e-06</v>
+        <v>2.4253711546521e-06</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.108049266868361e-06</v>
+        <v>4.10804926686836e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>4.806852583899458e-06</v>
+        <v>4.806852583899473e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>4.340901718231002e-06</v>
+        <v>4.34090171823099e-06</v>
       </c>
       <c r="G13" t="n">
-        <v>5.912651416039573e-06</v>
+        <v>5.912651416039601e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>5.610088420784146e-06</v>
+        <v>5.610088420784102e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>5.602721410214231e-06</v>
+        <v>5.602721410214294e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.444100445987452e-06</v>
+        <v>4.444100445987379e-06</v>
       </c>
       <c r="O13" t="n">
-        <v>4.762499547233882e-06</v>
+        <v>4.762499547233889e-06</v>
       </c>
       <c r="P13" t="n">
-        <v>4.684452233902419e-06</v>
+        <v>4.684452233902432e-06</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.814312076404227e-06</v>
+        <v>3.814312076404203e-06</v>
       </c>
       <c r="R13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>4.873247574470873e-06</v>
+        <v>4.873247574470884e-06</v>
       </c>
       <c r="V13" t="n">
-        <v>5.243417304195522e-06</v>
+        <v>5.243417304195447e-06</v>
       </c>
       <c r="W13" t="n">
-        <v>5.603015156384225e-06</v>
+        <v>5.603015156384199e-06</v>
       </c>
       <c r="X13" t="n">
-        <v>3.951301748463658e-06</v>
+        <v>3.951301748463644e-06</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.088935167612789e-06</v>
+        <v>7.088935167612762e-06</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.080284964417982e-06</v>
+        <v>4.080284964417967e-06</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.602721410214257e-06</v>
+        <v>5.602721410214306e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.164031446637334e-06</v>
+        <v>7.164031446637336e-06</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>1.643699534415515e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>1.643928654868654e-06</v>
+        <v>1.643928654868648e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.643699534415515e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.643699534415515e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>1.646948357407395e-06</v>
+        <v>1.646948357407388e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.643699534415514e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64403480572493e-06</v>
+        <v>1.644034805724925e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.643699534415515e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.643699534415515e-06</v>
+        <v>1.643699534415507e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.649879802191235e-06</v>
+        <v>1.649879802191227e-06</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.074444894725481e-06</v>
+        <v>2.074444894725474e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>1.976836037110031e-06</v>
+        <v>1.976836037110029e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>2.294320610234083e-06</v>
+        <v>2.294320610234075e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>1.790539987421113e-06</v>
+        <v>1.790539987421102e-06</v>
       </c>
       <c r="F15" t="n">
-        <v>1.974323939554867e-06</v>
+        <v>1.974323939554841e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.176640912870328e-06</v>
+        <v>2.176640912870253e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>2.059414721012853e-06</v>
+        <v>2.059414721012846e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.182281207159633e-06</v>
+        <v>2.182281207159628e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>2.111109052581276e-06</v>
+        <v>2.111109052581259e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>2.14043492346493e-06</v>
+        <v>2.140434923464913e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.026771528221039e-06</v>
+        <v>2.026771528221008e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>2.141453889417749e-06</v>
+        <v>2.141453889417716e-06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.029635422319298e-06</v>
+        <v>2.029635422319283e-06</v>
       </c>
       <c r="O15" t="n">
-        <v>2.012364258357443e-06</v>
+        <v>2.01236425835742e-06</v>
       </c>
       <c r="P15" t="n">
-        <v>1.986728201270011e-06</v>
+        <v>1.986728201269971e-06</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.012177873869665e-06</v>
+        <v>2.012177873869661e-06</v>
       </c>
       <c r="R15" t="n">
-        <v>2.049953405946227e-06</v>
+        <v>2.049953405946223e-06</v>
       </c>
       <c r="S15" t="n">
-        <v>2.061768170521929e-06</v>
+        <v>2.061768170521935e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>2.127464664397981e-06</v>
+        <v>2.127464664397974e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06002561820404e-06</v>
+        <v>2.060025618204023e-06</v>
       </c>
       <c r="V15" t="n">
-        <v>2.084410370246692e-06</v>
+        <v>2.084410370246678e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>2.328787765119557e-06</v>
+        <v>2.32878776511951e-06</v>
       </c>
       <c r="X15" t="n">
-        <v>2.045568548140602e-06</v>
+        <v>2.045568548140572e-06</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.062459221953893e-06</v>
+        <v>2.062459221953809e-06</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.111911545730553e-06</v>
+        <v>2.111911545730548e-06</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.177381995865373e-06</v>
+        <v>2.17738199586537e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.192993140974336e-06</v>
+        <v>2.192993140974328e-06</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.875671253190576e-06</v>
+        <v>3.87567125319057e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>4.574474570221686e-06</v>
+        <v>4.574474570221673e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>4.108523704553222e-06</v>
+        <v>4.108523704553213e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>5.674093134586067e-06</v>
+        <v>5.674093134586056e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.364392249213893e-06</v>
+        <v>5.364392249213878e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>5.370343396536447e-06</v>
+        <v>5.370343396536432e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.211722432309666e-06</v>
+        <v>4.211722432309658e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>4.523941265780383e-06</v>
+        <v>4.52394126578037e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>4.445893952448912e-06</v>
+        <v>4.445893952448906e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.581934062726444e-06</v>
+        <v>3.581934062726437e-06</v>
       </c>
       <c r="R16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="S16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>4.634689293017374e-06</v>
+        <v>4.634689293017362e-06</v>
       </c>
       <c r="V16" t="n">
-        <v>4.956043388866093e-06</v>
+        <v>4.956043388866079e-06</v>
       </c>
       <c r="W16" t="n">
-        <v>5.364456874930725e-06</v>
+        <v>5.364456874930709e-06</v>
       </c>
       <c r="X16" t="n">
-        <v>3.712743467010159e-06</v>
+        <v>3.712743467010154e-06</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.856557153934999e-06</v>
+        <v>6.856557153934987e-06</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.847906950740206e-06</v>
+        <v>3.847906950740197e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.370343396536473e-06</v>
+        <v>5.370343396536459e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.931653432959552e-06</v>
+        <v>6.931653432959536e-06</v>
       </c>
     </row>
   </sheetData>
@@ -9487,7 +9487,7 @@
         <v>1.402230504931317e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.712596758327333e-06</v>
+        <v>1.712596758327334e-06</v>
       </c>
       <c r="R2" t="n">
         <v>1.832920359342304e-06</v>
@@ -9660,7 +9660,7 @@
         <v>1.065582257735228e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.083253026783892e-06</v>
+        <v>1.083253026783891e-06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.196377881642457e-06</v>
@@ -9951,7 +9951,7 @@
         <v>1.932155197205298e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.105249838573903e-06</v>
+        <v>4.105249838573902e-06</v>
       </c>
       <c r="Z7" t="n">
         <v>2.02818377168138e-06</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide resource use mineral and metals results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.206567192973967e-06</v>
+        <v>1.206567192973201e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.115449161656777e-06</v>
+        <v>1.115449161656775e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.08384482695757e-06</v>
+        <v>1.083844826957287e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.361775334077959e-07</v>
+        <v>6.36177533407792e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.062026101316573e-06</v>
+        <v>1.062026101316571e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.416610332619056e-06</v>
+        <v>1.416610332618824e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.145694900099389e-06</v>
+        <v>1.145694900098979e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.125886151866438e-06</v>
+        <v>1.125886151867759e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.275640679461106e-06</v>
+        <v>1.27564067946094e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.219406808184625e-06</v>
+        <v>1.219406808184465e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.151948692937804e-06</v>
+        <v>1.151948692938047e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.315598231191532e-06</v>
+        <v>1.31559823119154e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.158133189080883e-06</v>
+        <v>1.158133189080578e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.263040135343412e-06</v>
+        <v>1.263040135343261e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.212986392555498e-06</v>
+        <v>1.212986392555197e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.125359193719717e-06</v>
+        <v>1.12535919371938e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.066497831327015e-06</v>
+        <v>1.06649783132682e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232745968591978e-06</v>
+        <v>1.232745968591994e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.116868425959322e-06</v>
+        <v>1.116868425959312e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33534539270564e-06</v>
+        <v>1.335345392705606e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.267655147561275e-06</v>
+        <v>1.267655147561273e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.458347088601574e-06</v>
+        <v>1.458347088601696e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.199362620279238e-06</v>
+        <v>1.19936262027878e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.324638067826447e-06</v>
+        <v>1.324638067825234e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.252345763571386e-06</v>
+        <v>1.252345763571581e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.21302707550672e-06</v>
+        <v>1.213027075506759e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.383530617315855e-06</v>
+        <v>1.383530617315853e-06</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.835459499208273e-06</v>
+        <v>4.835459499209575e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.734630418061343e-06</v>
+        <v>7.734630418061355e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.137851680791455e-06</v>
+        <v>6.137851680791456e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.267026281938062e-06</v>
+        <v>5.267026281938066e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.244304172450295e-06</v>
+        <v>8.244304172450102e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.650100353735241e-06</v>
+        <v>7.650100353734897e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.644999756994501e-06</v>
+        <v>7.64499975699451e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.470251091588317e-06</v>
+        <v>5.4702510915884e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.071698386081918e-06</v>
+        <v>6.07169838608018e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.924269121168307e-06</v>
+        <v>5.924269121166552e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.280597887463451e-06</v>
+        <v>4.280597887463115e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.280784604626472e-06</v>
+        <v>6.280784604628401e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.865423220339667e-06</v>
+        <v>6.865423220339674e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.659409648839002e-06</v>
+        <v>7.659409648838206e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.539367674540722e-06</v>
+        <v>4.539367674541631e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.046607768159996e-05</v>
+        <v>1.046607768160009e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.783013482475263e-06</v>
+        <v>4.783013482474913e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.658854770253378e-06</v>
+        <v>7.658854770252105e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.059029060784801e-05</v>
+        <v>1.059029060784803e-05</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.263158457021703e-07</v>
+        <v>9.263158457021677e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>9.412607072335423e-07</v>
+        <v>9.412607072332633e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>8.815849843679717e-07</v>
+        <v>8.815849843678141e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.072124622201529e-07</v>
+        <v>7.072124622200556e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.68366971382835e-07</v>
+        <v>8.683669713828196e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.002874103651732e-06</v>
+        <v>1.002874103652045e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.041286097479383e-07</v>
+        <v>9.041286097476041e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.96908553623093e-07</v>
+        <v>8.969085536225145e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.54795504459963e-07</v>
+        <v>9.547955044606408e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>9.309957346760808e-07</v>
+        <v>9.309957346758169e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>9.064080438017964e-07</v>
+        <v>9.064080438017558e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>9.572513552055897e-07</v>
+        <v>9.572513552054294e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>9.086622200239287e-07</v>
+        <v>9.086622200259635e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>9.468995700570601e-07</v>
+        <v>9.468995700570535e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.286555685715905e-07</v>
+        <v>9.286555685717689e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.967164835664692e-07</v>
+        <v>8.967164835662741e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.752622081593416e-07</v>
+        <v>8.752622081591767e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.358577020082324e-07</v>
+        <v>9.358577020076585e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>8.936216984214326e-07</v>
+        <v>8.936216984213312e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>9.732539873143927e-07</v>
+        <v>9.732539873140543e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>9.93918676884459e-07</v>
+        <v>9.939186768844567e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.018086661109627e-06</v>
+        <v>1.018086661109115e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>9.23689863555306e-07</v>
+        <v>9.236898635543252e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.693512931276858e-07</v>
+        <v>9.693512931261351e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.430015971258125e-07</v>
+        <v>9.430015971257918e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.286703970295876e-07</v>
+        <v>9.286703970294351e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.794815595184445e-07</v>
+        <v>9.794815595183105e-07</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.249004478719695e-06</v>
+        <v>2.249004478719202e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.353874548842459e-06</v>
+        <v>3.353874548842197e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.712508085021945e-06</v>
+        <v>2.712508085021758e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.401040159614278e-06</v>
+        <v>2.401040159614189e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.491488333441298e-06</v>
+        <v>3.491488333440308e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.278211203048235e-06</v>
+        <v>3.278211203048601e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.264243887775617e-06</v>
+        <v>3.264243887775635e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.480378560043001e-06</v>
+        <v>2.480378560041984e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.699599036335215e-06</v>
+        <v>2.699599036334384e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.645862800476037e-06</v>
+        <v>2.645862800475246e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.046763936752707e-06</v>
+        <v>2.046763936753965e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.77580850778037e-06</v>
+        <v>2.775808507780078e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.03423940710079e-06</v>
+        <v>3.034239407100787e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.278301147763236e-06</v>
+        <v>3.278301147763079e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.141082485514119e-06</v>
+        <v>2.141082485512527e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.301298688144606e-06</v>
+        <v>4.301298688143995e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.229888521472736e-06</v>
+        <v>2.229888521472743e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.278098901034489e-06</v>
+        <v>3.278098901035177e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.335237464833303e-06</v>
+        <v>4.33523746483319e-06</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.942573015914093e-07</v>
+        <v>6.942573015912311e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>7.092021631227806e-07</v>
+        <v>7.092021631227782e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>6.495264402572118e-07</v>
+        <v>6.495264402566458e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>4.751539181093915e-07</v>
+        <v>4.751539181093886e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.363084272720751e-07</v>
+        <v>6.363084272720737e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>7.653859280075884e-07</v>
+        <v>7.653859280076125e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.720700656371777e-07</v>
+        <v>6.72070065636672e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>6.648500095123316e-07</v>
+        <v>6.648500095118236e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.086464663632705e-07</v>
+        <v>7.086464663631592e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>6.989371905653201e-07</v>
+        <v>6.989371905656042e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>6.743494996910375e-07</v>
+        <v>6.743494996910659e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.251928110948302e-07</v>
+        <v>7.251928110948249e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>6.766036759131672e-07</v>
+        <v>6.766036759145542e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.094113944129165e-07</v>
+        <v>7.094113944131024e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>6.911673929274454e-07</v>
+        <v>6.911673929273381e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.646579394557087e-07</v>
+        <v>6.646579394560634e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>6.432036640485809e-07</v>
+        <v>6.43203664048249e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.037991578974728e-07</v>
+        <v>7.037991578974434e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>6.615631543106736e-07</v>
+        <v>6.615631543104051e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.357658116702471e-07</v>
+        <v>7.357658116703427e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>6.975799543065135e-07</v>
+        <v>6.975799543065128e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>7.80598485465485e-07</v>
+        <v>7.805984854658803e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>6.862016879111614e-07</v>
+        <v>6.862016879108491e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.37292749016929e-07</v>
+        <v>7.372927490149658e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.109430530150534e-07</v>
+        <v>7.109430530148628e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.966118529188273e-07</v>
+        <v>6.96611852918985e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.474230154076862e-07</v>
+        <v>7.474230154076826e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.016945934608935e-06</v>
+        <v>2.016945934608714e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.121816004731697e-06</v>
+        <v>3.121816004731699e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.480449540911183e-06</v>
+        <v>2.480449540911181e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.168981615503519e-06</v>
+        <v>2.168981615503518e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.254000157797155e-06</v>
+        <v>3.254000157796796e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.032062164951543e-06</v>
+        <v>3.03206216495222e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.032185343664858e-06</v>
+        <v>3.032185343664857e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.248320015932242e-06</v>
+        <v>2.248320015931298e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.462110860691071e-06</v>
+        <v>2.462110860690193e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.408374624831895e-06</v>
+        <v>2.408374624831012e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.814705392641947e-06</v>
+        <v>1.814705392643033e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.538320332136224e-06</v>
+        <v>2.538320332136563e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.737900684522843e-06</v>
+        <v>2.73790068452284e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.040812972119094e-06</v>
+        <v>3.040812972119365e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.903594309869974e-06</v>
+        <v>1.903594309868331e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.069240144033848e-06</v>
+        <v>4.069240144033743e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.997829977361977e-06</v>
+        <v>1.997829977361816e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.04604035692373e-06</v>
+        <v>3.046040356924257e-06</v>
       </c>
       <c r="AB7" t="n">
         <v>4.103178920722541e-06</v>
@@ -1270,82 +1270,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.778888988284378e-06</v>
+        <v>1.778888988282579e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.443856834289256e-06</v>
+        <v>1.443856834289259e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.19167484323353e-06</v>
+        <v>2.191674843231713e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.001944839518409e-06</v>
+        <v>1.00194483951841e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.467902203165934e-06</v>
+        <v>1.467902203165933e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.380901103563298e-06</v>
+        <v>2.380901103561534e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.868795474085044e-06</v>
+        <v>1.86879547408321e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.083590317022616e-06</v>
+        <v>2.083590317020744e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.974330120095639e-06</v>
+        <v>1.974330120095251e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.661427453247922e-06</v>
+        <v>1.661427453246111e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.684710989700847e-06</v>
+        <v>1.684710989698908e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.322330206814807e-06</v>
+        <v>2.32233020681471e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.587137440749603e-06</v>
+        <v>1.587137440750495e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.484056212803704e-06</v>
+        <v>1.484056212801834e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.402156076496944e-06</v>
+        <v>1.402156076496967e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.691590270646303e-06</v>
+        <v>1.691590270644417e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.878707984572531e-06</v>
+        <v>1.878707984570641e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.646759493957492e-06</v>
+        <v>1.646759493955856e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.770611327929659e-06</v>
+        <v>1.770611327928517e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64042778371337e-06</v>
+        <v>1.640427783711507e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.845152787559492e-06</v>
+        <v>1.845152787559491e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>2.602750928066188e-06</v>
+        <v>2.60275092806563e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.495830066542298e-06</v>
+        <v>1.495830066540413e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.154102956415202e-06</v>
+        <v>2.154102956413328e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.694661091341662e-06</v>
+        <v>1.694661091341034e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.982105848481177e-06</v>
+        <v>1.982105848480104e-06</v>
       </c>
       <c r="AB2" t="n">
         <v>2.260572042173987e-06</v>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.879665202174892e-06</v>
+        <v>4.87966520217347e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.787052755798509e-06</v>
+        <v>7.787052755798506e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.18413866660473e-06</v>
+        <v>6.184138666604734e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.311351535075649e-06</v>
+        <v>5.311351535075634e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.299629269212663e-06</v>
+        <v>8.299629269212531e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.702685894842029e-06</v>
+        <v>7.702685894841432e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.698642873394934e-06</v>
+        <v>7.69864287339496e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.516527436766068e-06</v>
+        <v>5.516527436765351e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.119936606890452e-06</v>
+        <v>6.119936606889129e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.972026438855462e-06</v>
+        <v>5.972026438853948e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.322993673770857e-06</v>
+        <v>4.322993673771241e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.329832952813739e-06</v>
+        <v>6.329832952813587e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.914408682487601e-06</v>
+        <v>6.914408682487597e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.71282686383383e-06</v>
+        <v>7.712826863833872e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.58260754833564e-06</v>
+        <v>4.58260754833436e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.052886918425101e-05</v>
+        <v>1.052886918425065e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.827048110496229e-06</v>
+        <v>4.827048110495334e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.712270175294688e-06</v>
+        <v>7.712270175294851e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.065364455212683e-05</v>
+        <v>1.065364455212684e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.237881856288614e-06</v>
+        <v>1.237881856286554e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.163291778353655e-06</v>
+        <v>1.163291778353645e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.388337453241329e-06</v>
+        <v>1.38833745323918e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.420780755077627e-07</v>
+        <v>9.420780755078328e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.118429647409589e-06</v>
+        <v>1.118429647409592e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.457308203124471e-06</v>
+        <v>1.457308203122404e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.270651714627537e-06</v>
+        <v>1.270651714625626e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.348941912630064e-06</v>
+        <v>1.348941912627985e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.309919498326753e-06</v>
+        <v>1.309919498326621e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.195068506070716e-06</v>
+        <v>1.195068506068754e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.203555081697956e-06</v>
+        <v>1.203555081696663e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.427299488655331e-06</v>
+        <v>1.427299488655395e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.167990668872305e-06</v>
+        <v>1.167990668871459e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.130418771727184e-06</v>
+        <v>1.130418771725144e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.100567133761783e-06</v>
+        <v>1.100567133761903e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.20606249882289e-06</v>
+        <v>1.20606249882075e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.274264708301782e-06</v>
+        <v>1.274264708299733e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18972220714921e-06</v>
+        <v>1.189722207147338e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.234864746288688e-06</v>
+        <v>1.234864746288697e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.187414373116092e-06</v>
+        <v>1.18741437311396e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.292894816582723e-06</v>
+        <v>1.292894816582754e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.538169859063451e-06</v>
+        <v>1.538169859062154e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.134710203159396e-06</v>
+        <v>1.134710203157233e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.374642941687417e-06</v>
+        <v>1.374642941685419e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.207181776905833e-06</v>
+        <v>1.207181776905262e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.311952015536204e-06</v>
+        <v>1.311952015535756e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.402316539162947e-06</v>
+        <v>1.402316539162855e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.368078375097257e-06</v>
+        <v>2.368078375097201e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.475312206176759e-06</v>
+        <v>3.475312206176645e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.830926873088642e-06</v>
+        <v>2.830926873088569e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.519321796829963e-06</v>
+        <v>2.519321796830008e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.614615118287611e-06</v>
+        <v>3.614615118287296e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.397837912472055e-06</v>
+        <v>3.397837912471933e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.386902323773215e-06</v>
+        <v>3.386902323773022e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.600207181192463e-06</v>
+        <v>2.600207181191981e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.820142738113775e-06</v>
+        <v>2.820142738113894e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.766231218715337e-06</v>
+        <v>2.76623121871394e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.165178139762043e-06</v>
+        <v>2.165178139761669e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.89664749147639e-06</v>
+        <v>2.896647491476014e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.140579064075979e-06</v>
+        <v>3.140579064075982e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.400732532109331e-06</v>
+        <v>3.400732532108489e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.259804348501153e-06</v>
+        <v>2.259804348499898e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.427146890262135e-06</v>
+        <v>4.427146890261984e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.348900063042268e-06</v>
+        <v>2.348900063041575e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.400529625672988e-06</v>
+        <v>3.400529625672986e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.461492912607262e-06</v>
+        <v>4.461492912607364e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.236476354497332e-07</v>
+        <v>9.236476354477212e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.49057557514867e-07</v>
+        <v>8.490575575148705e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.074103232402525e-06</v>
+        <v>1.074103232400513e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.27843854669049e-07</v>
+        <v>6.278438546690522e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.041954265708176e-07</v>
+        <v>8.041954265708195e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.135740344702622e-06</v>
+        <v>1.135740344700475e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>9.564174937888055e-07</v>
+        <v>9.564174937868086e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.03470769179111e-06</v>
+        <v>1.034707691789128e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.817312595700481e-07</v>
+        <v>9.81731259569639e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.808342852319823e-07</v>
+        <v>8.808342852299167e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.893208608591874e-07</v>
+        <v>8.893208608581029e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.113065267816582e-06</v>
+        <v>1.113065267816545e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>8.537564480335777e-07</v>
+        <v>8.537564480326333e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>8.088509133051074e-07</v>
+        <v>8.088509133031929e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.789992753396019e-07</v>
+        <v>7.789992753399596e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.918282779839349e-07</v>
+        <v>8.918282779819223e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>9.600304874629749e-07</v>
+        <v>9.600304874607633e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>8.754879863104799e-07</v>
+        <v>8.754879863084809e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>9.206305254498837e-07</v>
+        <v>9.206305254498581e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>8.658465146939443e-07</v>
+        <v>8.658465146920055e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>9.257400593010067e-07</v>
+        <v>9.257400593010084e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.216602000641535e-06</v>
+        <v>1.216602000640193e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>8.131423447373234e-07</v>
+        <v>8.131423447352665e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.060408720848558e-06</v>
+        <v>1.060408720846565e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.929475560669317e-07</v>
+        <v>8.929475560664469e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.977177946974333e-07</v>
+        <v>9.977177946970426e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.08808231832408e-06</v>
+        <v>1.088082318324082e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.053844154258562e-06</v>
+        <v>2.053844154258301e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.161077985337861e-06</v>
+        <v>3.161077985337865e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.516692652249793e-06</v>
+        <v>2.516692652249794e-06</v>
       </c>
       <c r="F7" t="n">
         <v>2.205087575991231e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.293047259865618e-06</v>
+        <v>3.293047259865326e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.069649673715469e-06</v>
+        <v>3.069649673715005e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.072668102934319e-06</v>
+        <v>3.072668102934318e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.285972960353804e-06</v>
+        <v>2.285972960353143e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.498574879691729e-06</v>
+        <v>2.498574879691929e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4446633602935e-06</v>
+        <v>2.444663360292003e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85094391892327e-06</v>
+        <v>1.850943918922838e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.575079633054409e-06</v>
+        <v>2.575079633054073e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.773424306794233e-06</v>
+        <v>2.773424306794234e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.079164673687244e-06</v>
+        <v>3.079164673686541e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.938236490079127e-06</v>
+        <v>1.938236490077954e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.112912669423209e-06</v>
+        <v>4.112912669423119e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.034665842203306e-06</v>
+        <v>2.034665842202741e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.08629540483408e-06</v>
+        <v>3.086295404834149e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.147258691768587e-06</v>
+        <v>4.147258691768579e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2955489652498e-06</v>
+        <v>1.295548965250734e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.184263313405979e-06</v>
+        <v>1.184263313406007e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.431296108726176e-06</v>
+        <v>1.431296108726114e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.771578328130528e-07</v>
+        <v>6.771578328140981e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.132428333418531e-06</v>
+        <v>1.13242833341857e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.505840834925952e-06</v>
+        <v>1.505840834925936e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.201800576767276e-06</v>
+        <v>1.201800576767311e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.185574267985329e-06</v>
+        <v>1.185574267985284e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.357198456808788e-06</v>
+        <v>1.35719845680874e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.330390763262958e-06</v>
+        <v>1.330390763263055e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.255133139874442e-06</v>
+        <v>1.255133139879843e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.357593506220046e-06</v>
+        <v>1.357593506220059e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.305760946043293e-06</v>
+        <v>1.305760946043298e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.229199941928368e-06</v>
+        <v>1.229199941928304e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.224745104418539e-06</v>
+        <v>1.224745104418601e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.279683491467969e-06</v>
+        <v>1.279683491468058e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.327444392687034e-06</v>
+        <v>1.327444392687024e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.321512658163034e-06</v>
+        <v>1.321512658163444e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.319300464553549e-06</v>
+        <v>1.319300464553633e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.396233291121481e-06</v>
+        <v>1.396233291121427e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.275917189171808e-06</v>
+        <v>1.275917189171691e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.554824967428253e-06</v>
+        <v>1.55482496742827e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.341952994096642e-06</v>
+        <v>1.341952994096496e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.386245996204104e-06</v>
+        <v>1.38624599620406e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.338820781170212e-06</v>
+        <v>1.338820781170439e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.333489039622329e-06</v>
+        <v>1.333489039622698e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.475068825626075e-06</v>
+        <v>1.4750688256261e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.841550238623687e-06</v>
+        <v>4.841550238623526e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.741599325545808e-06</v>
+        <v>7.741599325545756e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.14401242968509e-06</v>
+        <v>6.144012429685073e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.27306015333791e-06</v>
+        <v>5.273060153337917e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.251645830261333e-06</v>
+        <v>8.251645830261267e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.657008683676526e-06</v>
+        <v>7.657008683676507e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.651797352317614e-06</v>
+        <v>7.651797352317625e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.47657477575575e-06</v>
+        <v>5.476574775755702e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.078242778892381e-06</v>
+        <v>6.078242778892176e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.930759412957524e-06</v>
+        <v>5.930759412957448e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.286485013436982e-06</v>
+        <v>4.286485013436839e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.287399280230956e-06</v>
+        <v>6.287399280230803e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.871760105794015e-06</v>
+        <v>6.871760105794126e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.666536672250921e-06</v>
+        <v>7.666536672250865e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.54534975933871e-06</v>
+        <v>4.545349759338657e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.047422362327649e-05</v>
+        <v>1.047422362327633e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.789084976165397e-06</v>
+        <v>4.789084976165238e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.665981590048071e-06</v>
+        <v>7.665981590048039e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.059835706778015e-05</v>
+        <v>1.059835706778013e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.730761321532677e-07</v>
+        <v>9.730761321534583e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>9.805697776953803e-07</v>
+        <v>9.80569777695367e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.022554371926971e-06</v>
+        <v>1.022554371926964e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>7.362134266111501e-07</v>
+        <v>7.362134266113647e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.082165158703047e-07</v>
+        <v>9.082165158703183e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.049725049278417e-06</v>
+        <v>1.049725049278428e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.389059454005447e-07</v>
+        <v>9.389059454005459e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.32991646388459e-07</v>
+        <v>9.329916463884788e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.979229809777178e-07</v>
+        <v>9.979229809776856e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>9.857755583960171e-07</v>
+        <v>9.857755583960485e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>9.583450383905312e-07</v>
+        <v>9.583450383914028e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>9.866763891357678e-07</v>
+        <v>9.866763891357529e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>9.76798279237362e-07</v>
+        <v>9.767982792373866e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>9.488926922621748e-07</v>
+        <v>9.488926922621732e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.472689563011852e-07</v>
+        <v>9.472689563011927e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.672933532615887e-07</v>
+        <v>9.672933532618121e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>9.847016409191227e-07</v>
+        <v>9.847016409191109e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.825395933390699e-07</v>
+        <v>9.825395933391599e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>9.817332747452982e-07</v>
+        <v>9.817332747452991e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.009774386638451e-06</v>
+        <v>1.009774386638447e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.005682714909635e-06</v>
+        <v>1.005682714909839e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.067579190374779e-06</v>
+        <v>1.067579190374806e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>9.89989855764324e-07</v>
+        <v>9.899898557649286e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.006134134917803e-06</v>
+        <v>1.006134134917825e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.8884820093294e-07</v>
+        <v>9.888482009328801e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.869048437472069e-07</v>
+        <v>9.86904843747336e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.027082992286076e-06</v>
+        <v>1.027082992286107e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.26555195704882e-06</v>
+        <v>2.265551957048815e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.370641753993316e-06</v>
+        <v>3.370641753993277e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.72881773212326e-06</v>
+        <v>2.72881773212332e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.417428192477285e-06</v>
+        <v>2.417428192477306e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.508491756836598e-06</v>
+        <v>3.508491756836505e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.294129832564432e-06</v>
+        <v>3.294129832564468e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.280839780765192e-06</v>
+        <v>3.280839780765213e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.49701094399886e-06</v>
+        <v>2.497010943998853e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.716311865999773e-06</v>
+        <v>2.716311865999662e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.662555910953636e-06</v>
+        <v>2.662555910953535e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.063237200373213e-06</v>
+        <v>2.06323720037315e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.792546954698038e-06</v>
+        <v>2.792546954697981e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.045301748313352e-06</v>
+        <v>3.045301748313286e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.29522633944043e-06</v>
+        <v>3.295226339440406e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.157590360511084e-06</v>
+        <v>2.157590360511056e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.318595263564511e-06</v>
+        <v>4.318595263564357e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.246428984960999e-06</v>
+        <v>2.246428984960927e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.295024018495601e-06</v>
+        <v>3.295024018495446e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.352414425491878e-06</v>
+        <v>4.352414425491913e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.298319619564484e-07</v>
+        <v>7.298319619567217e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>7.373256074985633e-07</v>
+        <v>7.373256074985e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>7.793102017301503e-07</v>
+        <v>7.793102017300478e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>4.929692564143332e-07</v>
+        <v>4.929692564145994e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.649723456734866e-07</v>
+        <v>6.649723456735161e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.007438532731925e-07</v>
+        <v>8.00743853273151e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.956617752037266e-07</v>
+        <v>6.956617752036008e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>6.897474761916447e-07</v>
+        <v>6.897474761915279e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.410822326570455e-07</v>
+        <v>7.410822326569484e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>7.425313881991963e-07</v>
+        <v>7.425313881991282e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.15100868193712e-07</v>
+        <v>7.151008681939302e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.43432218938947e-07</v>
+        <v>7.434322189389937e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.335541090405452e-07</v>
+        <v>7.335541090404682e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>6.999114962569491e-07</v>
+        <v>6.999114962569038e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>6.98287760295959e-07</v>
+        <v>6.982877602958821e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.240491830647732e-07</v>
+        <v>7.240491830647206e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.414574707223021e-07</v>
+        <v>7.414574707221725e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.392954231422495e-07</v>
+        <v>7.39295423142197e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>7.384891045484812e-07</v>
+        <v>7.384891045484122e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.607931906332263e-07</v>
+        <v>7.607931906331757e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.03129774242031e-07</v>
+        <v>7.031297742418155e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.185979943695553e-07</v>
+        <v>8.185979943695819e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.410086597590982e-07</v>
+        <v>7.410086597593631e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.628899647209841e-07</v>
+        <v>7.628899647208788e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.456040307361221e-07</v>
+        <v>7.456040307365403e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.436606735503904e-07</v>
+        <v>7.436606735504098e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.838388220892593e-07</v>
+        <v>7.838388220892648e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.022307786852003e-06</v>
+        <v>2.022307786851846e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.127397583796496e-06</v>
+        <v>3.127397583796446e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298714e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.485573561926442e-06</v>
+        <v>2.485573561926445e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.174184022280463e-06</v>
+        <v>2.174184022280482e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.259510560831377e-06</v>
+        <v>3.259510560831289e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298716e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298716e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.037289084243753e-06</v>
+        <v>3.037289084243737e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298714e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298716e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.037595610568376e-06</v>
+        <v>3.037595610568404e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.253766773802043e-06</v>
+        <v>2.25376677380191e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.467330669994549e-06</v>
+        <v>2.467330669994409e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41357471494841e-06</v>
+        <v>2.413574714948285e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8199930301764e-06</v>
+        <v>1.819993030176213e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298716e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298714e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298716e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.54356575869281e-06</v>
+        <v>2.543565758692758e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.742748807645749e-06</v>
+        <v>2.742748807645958e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.046245143435198e-06</v>
+        <v>3.046245143435192e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.908609164505861e-06</v>
+        <v>1.908609164505849e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.075351093367695e-06</v>
+        <v>4.075351093367572e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.003184814764178e-06</v>
+        <v>2.003184814764068e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.051779848298778e-06</v>
+        <v>3.051779848298714e-06</v>
       </c>
       <c r="AB7" t="n">
         <v>4.109170255295059e-06</v>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.43084029966253e-06</v>
+        <v>1.43084029966256e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.335139004357071e-06</v>
+        <v>1.335139004357072e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62870406668031e-06</v>
+        <v>1.628704066680232e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>8.576379458296094e-07</v>
+        <v>8.576379458296105e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.217502915948911e-06</v>
+        <v>1.217502915948912e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.578253818545322e-06</v>
+        <v>1.578253818545248e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.318474574500764e-06</v>
+        <v>1.318474574500682e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.545466349861093e-06</v>
+        <v>1.54546634986101e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.462609191066287e-06</v>
+        <v>1.462609191065967e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.616021544349493e-06</v>
+        <v>1.616021544349415e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.373854457199717e-06</v>
+        <v>1.373854457199628e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.503616170488117e-06</v>
+        <v>1.503616170488119e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3785671553585e-06</v>
+        <v>1.378567155358417e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.240928789078239e-06</v>
+        <v>1.240928789078155e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.246417514328664e-06</v>
+        <v>1.246417514328588e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.350408654456268e-06</v>
+        <v>1.350408654456195e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.380184186321759e-06</v>
+        <v>1.380184186321686e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.444093454373407e-06</v>
+        <v>1.444093454373326e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.45759049960165e-06</v>
+        <v>1.457590499601567e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.404682449098934e-06</v>
+        <v>1.404682449098856e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.370542798981834e-06</v>
+        <v>1.370542798982033e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.752163059462114e-06</v>
+        <v>1.752163059461926e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.407116944711829e-06</v>
+        <v>1.407116944711747e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.343800681260875e-06</v>
+        <v>1.343800681260797e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.481724593931734e-06</v>
+        <v>1.481724593931648e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.488794300090482e-06</v>
+        <v>1.488794300090397e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.568507568759435e-06</v>
+        <v>1.568507568759413e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.858646686480161e-06</v>
+        <v>4.858646686480106e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.762267957161127e-06</v>
+        <v>7.762267957161135e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.162349885233866e-06</v>
+        <v>6.162349885233867e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.290365445287492e-06</v>
+        <v>5.29036544528749e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.272947702976585e-06</v>
+        <v>8.272947702976562e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.677337246032588e-06</v>
+        <v>7.677337246032681e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.672164956042939e-06</v>
+        <v>7.672164956042932e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.494454353555307e-06</v>
+        <v>5.494454353555312e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.096864350428536e-06</v>
+        <v>6.096864350428597e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.949199103899965e-06</v>
+        <v>5.949199103899957e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.302896939398371e-06</v>
+        <v>4.302896939398437e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.306329972899385e-06</v>
+        <v>6.306329972899541e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.89085035752872e-06</v>
+        <v>6.890850357528935e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.687116972050841e-06</v>
+        <v>7.687116972050894e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.562080924511367e-06</v>
+        <v>4.562080924511383e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.049835400092002e-05</v>
+        <v>1.049835400091994e-05</v>
       </c>
       <c r="Z3" t="n">
         <v>4.806116722398115e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.686561205310981e-06</v>
+        <v>7.686561205310951e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.062228481808462e-05</v>
+        <v>1.06222848180846e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.046900442433214e-06</v>
+        <v>1.04690044243317e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.060130973870055e-06</v>
+        <v>1.060130973870077e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.119019462077541e-06</v>
+        <v>1.119019462077458e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.262622706268215e-07</v>
+        <v>8.26262270626846e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.635252805971779e-07</v>
+        <v>9.635252805972039e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.100630939049059e-06</v>
+        <v>1.100630939048974e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.005944455076714e-06</v>
+        <v>1.005944455076635e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.088680291723551e-06</v>
+        <v>1.088680291723467e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.060818941320312e-06</v>
+        <v>1.06081894132032e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.114396831613652e-06</v>
+        <v>1.114396831613569e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.026129772017067e-06</v>
+        <v>1.026129772016983e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.064277407312635e-06</v>
+        <v>1.064277407312654e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.027847495156648e-06</v>
+        <v>1.02784749515657e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.776799268787886e-07</v>
+        <v>9.776799268787111e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.796805027807055e-07</v>
+        <v>9.796805027806238e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.017584052231596e-06</v>
+        <v>1.017584052231515e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.028436883954622e-06</v>
+        <v>1.028436883954541e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05173106169893e-06</v>
+        <v>1.051731061698847e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.056650576194312e-06</v>
+        <v>1.056650576194238e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.03736621306377e-06</v>
+        <v>1.037366213063692e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.065123606339316e-06</v>
+        <v>1.065123606339621e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16401881521782e-06</v>
+        <v>1.164018815217728e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.038253558127384e-06</v>
+        <v>1.0382535581273e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.015175523596614e-06</v>
+        <v>1.015175523596536e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.065447170180788e-06</v>
+        <v>1.065447170180714e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.068023995058972e-06</v>
+        <v>1.068023995058886e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.085468019829414e-06</v>
+        <v>1.08546801982941e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.296295619093449e-06</v>
+        <v>2.296295619093373e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.402744006008596e-06</v>
+        <v>3.402744006008621e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.759767481467136e-06</v>
+        <v>2.75976748146716e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.448035846574638e-06</v>
+        <v>2.448035846574662e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.540768246859647e-06</v>
+        <v>3.540768246859739e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.326014340334332e-06</v>
+        <v>3.326014340334336e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.312641004890448e-06</v>
+        <v>3.312641004890478e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.528040047711759e-06</v>
+        <v>2.528040047711839e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.74761141771674e-06</v>
+        <v>2.747611417716798e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.693789169329931e-06</v>
+        <v>2.693789169329891e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.093731362225142e-06</v>
+        <v>2.093731362225117e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.823959177437826e-06</v>
+        <v>2.823959177437859e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.077210888705541e-06</v>
+        <v>3.077210888705326e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.327239824608976e-06</v>
+        <v>3.327239824609049e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.188200881306823e-06</v>
+        <v>2.18820088130692e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.351902710419932e-06</v>
+        <v>4.351902710419855e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.277149064023519e-06</v>
+        <v>2.277149064023501e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.327037254158442e-06</v>
+        <v>3.327037254158521e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.385463512388375e-06</v>
+        <v>4.385463512388372e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.875759377630757e-07</v>
+        <v>7.875759377629814e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.008064691999232e-07</v>
+        <v>8.008064691999245e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>8.596949574073989e-07</v>
+        <v>8.596949574073076e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.669377659566902e-07</v>
+        <v>5.669377659566921e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.042007759270483e-07</v>
+        <v>7.042007759270503e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.34518685484146e-07</v>
+        <v>8.345186854840446e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.46619950406575e-07</v>
+        <v>7.466199504064789e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>8.293557870534127e-07</v>
+        <v>8.293557870533158e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.86758951459155e-07</v>
+        <v>7.867589514593221e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.550723269435115e-07</v>
+        <v>8.550723269434186e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.668052673469264e-07</v>
+        <v>7.668052673468311e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>8.049529026425024e-07</v>
+        <v>8.049529026425035e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.685229904865066e-07</v>
+        <v>7.685229904864133e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.11567673313876e-07</v>
+        <v>7.115676733137745e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.135682492157933e-07</v>
+        <v>7.13568249215688e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.582595475614605e-07</v>
+        <v>7.582595475613626e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.691123792844928e-07</v>
+        <v>7.691123792843878e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.924065570287906e-07</v>
+        <v>7.924065570286862e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>7.973260715241791e-07</v>
+        <v>7.973260715240805e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.71253959498858e-07</v>
+        <v>7.712539594987579e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.446684201122016e-07</v>
+        <v>7.446684201124267e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.979065616529054e-07</v>
+        <v>8.979065616527927e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.721413045624692e-07</v>
+        <v>7.721413045623634e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.558510189264732e-07</v>
+        <v>7.558510189263753e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.061226655106519e-07</v>
+        <v>8.061226655105502e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.086994903888313e-07</v>
+        <v>8.086994903887366e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.261435151592577e-07</v>
+        <v>8.261435151592536e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.036971114423315e-06</v>
+        <v>2.036971114423218e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.14341950133846e-06</v>
+        <v>3.143419501338464e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.500442976797007e-06</v>
+        <v>2.500442976797006e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.188711341904508e-06</v>
+        <v>2.188711341904509e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.274655993294732e-06</v>
+        <v>3.274655993294806e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.051954350473336e-06</v>
+        <v>3.05195435047337e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.053316500220317e-06</v>
+        <v>3.053316500220319e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.268715543041627e-06</v>
+        <v>2.268715543041681e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.481499164151828e-06</v>
+        <v>2.481499164151869e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42767691576502e-06</v>
+        <v>2.427676915764954e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.834406857555014e-06</v>
+        <v>1.834406857554967e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.557846923872917e-06</v>
+        <v>2.557846923872925e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.756755702478406e-06</v>
+        <v>2.756755702478475e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.061127571044065e-06</v>
+        <v>3.061127571044117e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.92208862774191e-06</v>
+        <v>1.922088627741985e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.092578205749802e-06</v>
+        <v>4.0925782057497e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.017824559353385e-06</v>
+        <v>2.017824559353349e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.067712749488305e-06</v>
+        <v>3.06771274948836e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.126139007718224e-06</v>
+        <v>4.126139007718217e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.456309916284775e-06</v>
+        <v>1.456309916284747e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.347104554633732e-06</v>
+        <v>1.347104554633728e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.872548958540784e-06</v>
+        <v>1.87254895854076e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.001503409806735e-07</v>
+        <v>9.001503409806733e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.257758666336311e-06</v>
+        <v>1.257758666336314e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.661473280280689e-06</v>
+        <v>1.661473280280924e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.427856819058396e-06</v>
+        <v>1.427856819058364e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.660451075321752e-06</v>
+        <v>1.660451075321722e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.527666427330645e-06</v>
+        <v>1.52766642733059e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.581233336306028e-06</v>
+        <v>1.581233336305998e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.366061130196499e-06</v>
+        <v>1.366061130196486e-06</v>
       </c>
       <c r="M2" t="n">
         <v>1.568642553105788e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.371482668149597e-06</v>
+        <v>1.371482668149567e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.350486879707934e-06</v>
+        <v>1.350486879707903e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.301956154863617e-06</v>
+        <v>1.301956154863603e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.338434392536246e-06</v>
+        <v>1.338434392536211e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.409945933753466e-06</v>
+        <v>1.409945933753437e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.432312052176747e-06</v>
+        <v>1.432312052176717e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55667979159395e-06</v>
+        <v>1.556679791593925e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.440712936411272e-06</v>
+        <v>1.440712936411243e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.463192113995204e-06</v>
+        <v>1.463192113995141e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.949497175580205e-06</v>
+        <v>1.949497175580173e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.413344761698971e-06</v>
+        <v>1.413344761698943e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.433620257521407e-06</v>
+        <v>1.433620257521388e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.527236725527055e-06</v>
+        <v>1.527236725527033e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.651176549427813e-06</v>
+        <v>1.651176549427786e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.662472527288486e-06</v>
+        <v>1.662472527288484e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.866148663594997e-06</v>
+        <v>4.866148663594976e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.771234886212464e-06</v>
+        <v>7.77123488621246e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.170319726298552e-06</v>
+        <v>6.170319726298545e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.297937747100542e-06</v>
+        <v>5.297937747100536e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.282378002458854e-06</v>
+        <v>8.282378002458818e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.686343290856032e-06</v>
+        <v>7.686343290856051e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.681140574475463e-06</v>
+        <v>7.681140574475461e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.502315420901414e-06</v>
+        <v>5.502315420901394e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.105065645733806e-06</v>
+        <v>6.105065645733758e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.957317001111544e-06</v>
+        <v>5.957317001111511e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.31008504123932e-06</v>
+        <v>4.310085041239294e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.314718870430482e-06</v>
+        <v>6.314718870430443e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.899380347043225e-06</v>
+        <v>6.89938034704318e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.696216407175109e-06</v>
+        <v>7.696216407175077e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.569415407783388e-06</v>
+        <v>4.569415407783363e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.050915971431637e-05</v>
+        <v>1.050915971431633e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.813589031740644e-06</v>
+        <v>4.813589031740612e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.695660326553966e-06</v>
+        <v>7.695660326553934e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.063306492286095e-05</v>
+        <v>1.063306492286094e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.070676155725162e-06</v>
+        <v>1.07067615572514e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.078900603861738e-06</v>
+        <v>1.078900603861719e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.222390398901893e-06</v>
+        <v>1.222390398901847e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.560726653602363e-07</v>
+        <v>8.560726653602308e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.925769324540393e-07</v>
+        <v>9.92576932454019e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.145455792751812e-06</v>
+        <v>1.145455792751892e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.060305335899279e-06</v>
+        <v>1.060305335899261e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.145083211047605e-06</v>
+        <v>1.145083211047602e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.099331247914084e-06</v>
+        <v>1.099331247914044e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.116209275398057e-06</v>
+        <v>1.116209275398026e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.037781532950698e-06</v>
+        <v>1.037781532950722e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.102392609824608e-06</v>
+        <v>1.102392609824536e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.039757619871724e-06</v>
+        <v>1.039757619871703e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.032104901529749e-06</v>
+        <v>1.032104901529715e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.014416022200535e-06</v>
+        <v>1.01441602220051e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02771191148309e-06</v>
+        <v>1.027711911483084e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.053777028525865e-06</v>
+        <v>1.053777028525848e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.061929216054914e-06</v>
+        <v>1.061929216054909e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1072597966728e-06</v>
+        <v>1.107259796672755e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.064991239710271e-06</v>
+        <v>1.064991239710232e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.115698009641728e-06</v>
+        <v>1.115698009642266e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25043712044115e-06</v>
+        <v>1.250437120441133e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.055015861400962e-06</v>
+        <v>1.055015861400932e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.062406041541333e-06</v>
+        <v>1.06240604154132e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.096528144829333e-06</v>
+        <v>1.096528144829309e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.141702755266261e-06</v>
+        <v>1.141702755266242e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.134217509317006e-06</v>
+        <v>1.134217509316962e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.313522338771641e-06</v>
+        <v>2.313522338771594e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.420420673775218e-06</v>
+        <v>3.420420673775217e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.77698752085523e-06</v>
+        <v>2.776987520855216e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.465174765214565e-06</v>
+        <v>2.465174765214553e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.558697817397263e-06</v>
+        <v>3.558697817397228e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.344096645834186e-06</v>
+        <v>3.344096645834174e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.330326362038286e-06</v>
+        <v>3.330326362038347e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.545397651562613e-06</v>
+        <v>2.545397651562563e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.765093030663484e-06</v>
+        <v>2.765093030663473e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.711240384650865e-06</v>
+        <v>2.711240384650838e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.110843678051714e-06</v>
+        <v>2.110843678051668e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.841509169192992e-06</v>
+        <v>2.841509169192958e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.097124785642587e-06</v>
+        <v>3.09712478564314e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.345048798973291e-06</v>
+        <v>3.345048798973272e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.205366551446092e-06</v>
+        <v>2.205366551446071e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.370333603178282e-06</v>
+        <v>4.370333603178262e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.294364970147074e-06</v>
+        <v>2.294364970147036e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.344846114116712e-06</v>
+        <v>3.344846114116688e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.403893099488945e-06</v>
+        <v>4.403893099488925e-06</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.004291281550682e-07</v>
+        <v>8.004291281550402e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.086535762916227e-07</v>
+        <v>8.086535762916203e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>9.521433713317784e-07</v>
+        <v>9.521433713317514e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.858256377901319e-07</v>
+        <v>5.858256377901332e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.223299048839199e-07</v>
+        <v>7.223299048839182e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.680213425444377e-07</v>
+        <v>8.680213425442503e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.900583083291906e-07</v>
+        <v>7.900583083291596e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>8.748361834775342e-07</v>
+        <v>8.748361834775016e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.135956888967884e-07</v>
+        <v>8.135956888966727e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.459622478279574e-07</v>
+        <v>8.459622478279279e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.675345053806412e-07</v>
+        <v>7.675345053806211e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>8.321455822545096e-07</v>
+        <v>8.321455822542662e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.695105923016318e-07</v>
+        <v>7.695105923016049e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.546704513221037e-07</v>
+        <v>7.546704513220703e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.36981571992893e-07</v>
+        <v>7.369815719928644e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.574648839130079e-07</v>
+        <v>7.574648839129827e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.835300009557786e-07</v>
+        <v>7.835300009557475e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.916821884848459e-07</v>
+        <v>7.916821884848108e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>8.370127691026847e-07</v>
+        <v>8.370127691026546e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.875567895026167e-07</v>
+        <v>7.875567895025893e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.814927843275567e-07</v>
+        <v>7.814927843274979e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>9.730026702335244e-07</v>
+        <v>9.730026702334908e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.77581411193304e-07</v>
+        <v>7.77581411193287e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.921590139712489e-07</v>
+        <v>7.921590139712211e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.262811172592482e-07</v>
+        <v>8.2628111725921e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.714557276961711e-07</v>
+        <v>8.714557276961431e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.639704817468647e-07</v>
+        <v>8.639704817468642e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.043275311201514e-06</v>
+        <v>2.043275311201498e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.150173646205123e-06</v>
+        <v>3.150173646205115e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.506740493285125e-06</v>
+        <v>2.506740493285112e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.194927737644467e-06</v>
+        <v>2.194927737644457e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.28126336718961e-06</v>
+        <v>3.281263367189587e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.058361086816765e-06</v>
+        <v>3.058361086816729e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.060079334468144e-06</v>
+        <v>3.060079334467858e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.275150623992485e-06</v>
+        <v>2.275150623992463e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.487658580455867e-06</v>
+        <v>2.487658580455835e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.433805934443229e-06</v>
+        <v>2.433805934443203e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.840596650481596e-06</v>
+        <v>1.840596650481572e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.564074718985357e-06</v>
+        <v>2.564074718985315e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.762919560328315e-06</v>
+        <v>2.762919560328384e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.067614348765651e-06</v>
+        <v>3.067614348765626e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.927932101238464e-06</v>
+        <v>1.92793210123843e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.100086575608195e-06</v>
+        <v>4.100086575608168e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.024117942576975e-06</v>
+        <v>2.02411794257694e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.074599086546634e-06</v>
+        <v>3.074599086546593e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.133646071918831e-06</v>
+        <v>4.133646071918823e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.560719333270066e-06</v>
+        <v>1.56071933327006e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.210641164729973e-06</v>
+        <v>1.210641164729955e-06</v>
       </c>
       <c r="D2" t="n">
         <v>1.944021911470968e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.996846630225426e-07</v>
+        <v>6.996846630225332e-07</v>
       </c>
       <c r="F2" t="n">
         <v>1.218100972678851e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.68798903976622e-06</v>
+        <v>1.687989039766212e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.57481923075457e-06</v>
+        <v>1.574819230754557e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.267945002056227e-06</v>
+        <v>1.26794500205623e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.476319395646173e-06</v>
+        <v>1.476319395646164e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.446154361197019e-06</v>
+        <v>1.446154361197022e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.502180322398054e-06</v>
+        <v>1.502180322398055e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.410357789097943e-06</v>
+        <v>1.410357789097938e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.365760416914116e-06</v>
+        <v>1.365760416914113e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25513943904498e-06</v>
+        <v>1.255139439044969e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.263596400286467e-06</v>
+        <v>1.263596400286466e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.431839188352345e-06</v>
+        <v>1.431839188352347e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.478397010278197e-06</v>
+        <v>1.478397010278196e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.414471708239995e-06</v>
+        <v>1.414471708239993e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.391932705883783e-06</v>
+        <v>1.391932705883776e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.380228784273153e-06</v>
+        <v>1.380228784273152e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.373810273193103e-06</v>
+        <v>1.373810273193093e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.685255494657153e-06</v>
+        <v>1.685255494657152e-06</v>
       </c>
       <c r="X2" t="n">
         <v>1.400965481898014e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.413624710265897e-06</v>
+        <v>1.413624710265896e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.462334253598346e-06</v>
+        <v>1.462334253598337e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.386784339411626e-06</v>
+        <v>1.386784339411608e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.505245869746673e-06</v>
+        <v>1.505245869746654e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.847974802602224e-06</v>
+        <v>4.847974802602209e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.748854255419243e-06</v>
+        <v>7.748854255419235e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.150363598334946e-06</v>
+        <v>6.150363598334942e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.279237442091861e-06</v>
+        <v>5.279237442091836e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.259737084391412e-06</v>
+        <v>8.259737084391381e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.664525997575945e-06</v>
+        <v>7.664525997575931e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.65902686618999e-06</v>
+        <v>7.659026866189992e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.483309709079864e-06</v>
+        <v>5.48330970907985e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.085271778496676e-06</v>
+        <v>6.085271778496648e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.937716329811249e-06</v>
+        <v>5.937716329811238e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.292638288323074e-06</v>
+        <v>4.292638288323064e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.294640122375662e-06</v>
+        <v>6.294640122375651e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.878685666862962e-06</v>
+        <v>6.87868566686292e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.674341953256402e-06</v>
+        <v>7.674341953256399e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.551629554815739e-06</v>
+        <v>4.551629554815719e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.04835886888521e-05</v>
+        <v>1.048358868885209e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.795483897656325e-06</v>
+        <v>4.795483897656318e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.673786599762455e-06</v>
+        <v>7.673786599762476e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.060693937896423e-05</v>
+        <v>1.060693937896418e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.093795550992895e-06</v>
+        <v>1.093795550992884e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.013902546044239e-06</v>
+        <v>1.013902546044233e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.233504839781013e-06</v>
+        <v>1.233504839781017e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>7.680353228808863e-07</v>
+        <v>7.680353228808827e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.632173025900796e-07</v>
+        <v>9.63217302590069e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.140183864534397e-06</v>
+        <v>1.140183864534399e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.098934798056642e-06</v>
+        <v>1.098934798056639e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>9.870827451952216e-07</v>
+        <v>9.87082745195236e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.064130967277631e-06</v>
+        <v>1.064130967277636e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.052037963962093e-06</v>
+        <v>1.052037963962098e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.072458768929819e-06</v>
+        <v>1.072458768929827e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.029610549773779e-06</v>
+        <v>1.029610549773776e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.022735315304331e-06</v>
+        <v>1.02273531530434e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>9.824152678481323e-07</v>
+        <v>9.824152678481315e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.854977309140146e-07</v>
+        <v>9.854977309140171e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.046820251557455e-06</v>
+        <v>1.046820251557461e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.063790030939882e-06</v>
+        <v>1.063790030939881e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.040490008995752e-06</v>
+        <v>1.04049000899576e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.032274807303241e-06</v>
+        <v>1.032274807303225e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.028008865310553e-06</v>
+        <v>1.02800886531056e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.057728034175298e-06</v>
+        <v>1.057728034175269e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13918751944106e-06</v>
+        <v>1.139187519441049e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.035567148092217e-06</v>
+        <v>1.035567148092228e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.040181288180146e-06</v>
+        <v>1.040181288180155e-06</v>
       </c>
       <c r="Z4" t="n">
         <v>1.057935344748488e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03039828817931e-06</v>
+        <v>1.030398288179318e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.061727685995908e-06</v>
+        <v>1.061727685995882e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.291961568661878e-06</v>
+        <v>2.291961568661876e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.397004442026131e-06</v>
+        <v>3.397004442026124e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.754743789698722e-06</v>
+        <v>2.754743789698707e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.44345385741902e-06</v>
+        <v>2.443453857419008e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.535508857438626e-06</v>
+        <v>3.535508857438613e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.319659608090382e-06</v>
+        <v>3.319659608090355e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.307177052796952e-06</v>
+        <v>3.307177052796945e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.523533681593835e-06</v>
+        <v>2.523533681593836e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.742941787300763e-06</v>
+        <v>2.742941787300775e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.689159558938482e-06</v>
+        <v>2.689159558938485e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.089547930297703e-06</v>
+        <v>2.08954793029769e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.819254090117434e-06</v>
+        <v>2.819254090117439e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.064190473657477e-06</v>
+        <v>3.064190473657463e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.322139206196604e-06</v>
+        <v>3.32213920619661e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.18394720570529e-06</v>
+        <v>2.18394720570526e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.346076653480577e-06</v>
+        <v>4.346076653480553e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.272829250188413e-06</v>
+        <v>2.272829250188421e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.321936786369354e-06</v>
+        <v>3.321936786369349e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.379188092624504e-06</v>
+        <v>4.379188092624526e-06</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.292967286386332e-07</v>
+        <v>8.292967286386216e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>7.494037236899754e-07</v>
+        <v>7.494037236899577e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>9.690060174267518e-07</v>
+        <v>9.690060174267429e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.035365005266243e-07</v>
+        <v>5.035365005266183e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.987184802358168e-07</v>
+        <v>6.98718480235817e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.698369072628022e-07</v>
+        <v>8.698369072627987e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>8.344359757023801e-07</v>
+        <v>8.344359757023745e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>7.22583922840959e-07</v>
+        <v>7.225839228409665e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.870253650594806e-07</v>
+        <v>7.870253650594747e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>7.875391416078306e-07</v>
+        <v>7.875391416078338e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.079599465755564e-07</v>
+        <v>8.079599465755534e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.651117274195182e-07</v>
+        <v>7.651117274195164e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.582364929500682e-07</v>
+        <v>7.582364929500655e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.120683105765372e-07</v>
+        <v>7.120683105765295e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.151507736424184e-07</v>
+        <v>7.151507736424127e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.82321429203193e-07</v>
+        <v>7.823214292031912e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.99291208585619e-07</v>
+        <v>7.992912085856184e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.759911866414896e-07</v>
+        <v>7.759911866414868e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>7.677759849489783e-07</v>
+        <v>7.67775984948964e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.576619080389566e-07</v>
+        <v>7.576619080389539e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.411266388712317e-07</v>
+        <v>7.411266388712383e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.688405621694649e-07</v>
+        <v>8.688405621694462e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.652201908206208e-07</v>
+        <v>7.652201908206196e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.756824658258836e-07</v>
+        <v>7.756824658258807e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.93436522394226e-07</v>
+        <v>7.934365223942201e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.658994658250484e-07</v>
+        <v>7.658994658250329e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.972288636416449e-07</v>
+        <v>7.972288636416296e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.027462746307614e-06</v>
+        <v>2.027462746307611e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.132505619671866e-06</v>
+        <v>3.132505619671858e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.49024496734446e-06</v>
+        <v>2.490244967344442e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.178955035064756e-06</v>
+        <v>2.178955035064748e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.265161900167029e-06</v>
+        <v>3.265161900167022e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.042554005872235e-06</v>
+        <v>3.042554005872219e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.042678230442691e-06</v>
+        <v>3.042678230442688e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.259034859239575e-06</v>
+        <v>2.259034859239563e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.472594830029166e-06</v>
+        <v>2.472594830029159e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.418812601666886e-06</v>
+        <v>2.418812601666894e-06</v>
       </c>
       <c r="Q7" t="n">
         <v>1.825049107943441e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.548907132845839e-06</v>
+        <v>2.548907132845821e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.747589078353413e-06</v>
+        <v>2.7475890783534e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.051792248925007e-06</v>
+        <v>3.051792248924994e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.913600248433693e-06</v>
+        <v>1.913600248433676e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.081577831126315e-06</v>
+        <v>4.081577831126313e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.00833042783415e-06</v>
+        <v>2.008330427834156e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.057437964015088e-06</v>
+        <v>3.057437964015064e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.114689270270242e-06</v>
+        <v>4.114689270270251e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.792491839156363e-06</v>
+        <v>1.792491839156153e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.410314642267924e-06</v>
+        <v>1.410314642267915e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.23702135064887e-06</v>
+        <v>2.237021350648659e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.051721529596472e-06</v>
+        <v>1.051721529596461e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.456306227861744e-06</v>
+        <v>1.456306227861736e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.042976278673767e-06</v>
+        <v>2.04297627867329e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81111849745388e-06</v>
+        <v>1.811118497453669e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.987839146463784e-06</v>
+        <v>1.987839146463575e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.817905705353887e-06</v>
+        <v>1.817905705353695e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.237561622048056e-06</v>
+        <v>2.237561622047845e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>2.119449304234436e-06</v>
+        <v>2.11944930423423e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.111227901252808e-06</v>
+        <v>2.111227901252796e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.555664681298985e-06</v>
+        <v>1.55566468129879e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.353749466957408e-06</v>
+        <v>1.353749466957197e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.402230504931332e-06</v>
+        <v>1.402230504931124e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.712596758327346e-06</v>
+        <v>1.712596758327174e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.832920359342321e-06</v>
+        <v>1.832920359342104e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.648684379062982e-06</v>
+        <v>1.648684379062775e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.664608405125478e-06</v>
+        <v>1.664608405125565e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.626730572153788e-06</v>
+        <v>1.626730572153572e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65596898067733e-06</v>
+        <v>1.655968980676889e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.97333021909281e-06</v>
+        <v>1.973330219092597e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.459997263210128e-06</v>
+        <v>1.459997263209926e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.833831946479377e-06</v>
+        <v>1.83383194647916e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.740101008364244e-06</v>
+        <v>1.740101008364032e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.966115265786113e-06</v>
+        <v>1.966115265785908e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.915585947151636e-06</v>
+        <v>1.915585947151618e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.87190348167587e-06</v>
+        <v>4.871903481675694e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.777537481839192e-06</v>
+        <v>7.77753748183915e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.175863258490001e-06</v>
+        <v>6.175863258489961e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.303412832687493e-06</v>
+        <v>5.30341283268747e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.289913735566819e-06</v>
+        <v>8.28991373556682e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.693218202731419e-06</v>
+        <v>7.693218202731155e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.688758674560946e-06</v>
+        <v>7.688758674560907e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.508401879168168e-06</v>
+        <v>5.508401879168022e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.111466323806806e-06</v>
+        <v>6.111466323806486e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.963640656317811e-06</v>
+        <v>5.963640656317699e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.315549977712704e-06</v>
+        <v>4.315549977712683e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.321253236651795e-06</v>
+        <v>6.321253236651687e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.905333078533993e-06</v>
+        <v>6.905333078533687e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.703446568287305e-06</v>
+        <v>7.703446568286958e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.575015535804182e-06</v>
+        <v>4.575015535804054e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.051789802201297e-05</v>
+        <v>1.051789802201282e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.819316449953157e-06</v>
+        <v>4.819316449953139e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.702890197783153e-06</v>
+        <v>7.702890197782823e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.064148948467138e-05</v>
+        <v>1.064148948467133e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.225498700428853e-06</v>
+        <v>1.225498700428649e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.133638825484512e-06</v>
+        <v>1.133638825484467e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.387524487438801e-06</v>
+        <v>1.3875244874386e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.430342220630106e-07</v>
+        <v>9.430342220629885e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.096909557264332e-06</v>
+        <v>1.096909557264315e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.316797337296136e-06</v>
+        <v>1.316797337295853e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.232287898653024e-06</v>
+        <v>1.232287898652822e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.29670050005851e-06</v>
+        <v>1.296700500058301e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.235329793616265e-06</v>
+        <v>1.235329793616215e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.387721410019604e-06</v>
+        <v>1.387721410019414e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34467085712141e-06</v>
+        <v>1.34467085712121e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.332693503326771e-06</v>
+        <v>1.332693503326751e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.139177982354731e-06</v>
+        <v>1.139177982354533e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.065582257735377e-06</v>
+        <v>1.065582257735176e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.083253026783779e-06</v>
+        <v>1.083253026783585e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.19637788164207e-06</v>
+        <v>1.196377881642147e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.240234421300976e-06</v>
+        <v>1.240234421300776e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.173082569897264e-06</v>
+        <v>1.173082569897069e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.178886690407686e-06</v>
+        <v>1.17888669040767e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.165080665073468e-06</v>
+        <v>1.16508066507327e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.205316695269358e-06</v>
+        <v>1.20531669526896e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.291412166404215e-06</v>
+        <v>1.291412166404008e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.104308331844888e-06</v>
+        <v>1.104308331844681e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.240566684108033e-06</v>
+        <v>1.240566684107835e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.206402857809315e-06</v>
+        <v>1.206402857809114e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.288782400646176e-06</v>
+        <v>1.288782400645983e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.258542593124705e-06</v>
+        <v>1.258542593124679e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.347908083850027e-06</v>
+        <v>2.347908083849537e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.45441678280281e-06</v>
+        <v>3.454416782802736e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.810723711534625e-06</v>
+        <v>2.810723711534597e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.49913473971677e-06</v>
+        <v>2.499134739716744e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.593732685090485e-06</v>
+        <v>3.59373268509023e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.376812207507765e-06</v>
+        <v>3.37681220750768e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.365637975524561e-06</v>
+        <v>3.365637975524534e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.579904275594441e-06</v>
+        <v>2.579904275594369e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.799714184124972e-06</v>
+        <v>2.799714184124922e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.745833464181865e-06</v>
+        <v>2.745833464181751e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14512376468816e-06</v>
+        <v>2.145123764688015e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.876179050414689e-06</v>
+        <v>2.876179050414526e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.118648267792655e-06</v>
+        <v>3.118648267792358e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.379972289262294e-06</v>
+        <v>3.379972289262108e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.239695913814095e-06</v>
+        <v>2.23969591381381e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.405806795187741e-06</v>
+        <v>4.405806795187541e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.328740728295215e-06</v>
+        <v>2.328740728295113e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.379769498746768e-06</v>
+        <v>3.379769498746465e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.439031967818079e-06</v>
+        <v>4.439031967818052e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.249417438150162e-07</v>
+        <v>9.249417438148402e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.330818688706906e-07</v>
+        <v>8.330818688706727e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.086967530824966e-06</v>
+        <v>1.086967530824786e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.424772654491879e-07</v>
+        <v>6.42477265449179e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.963526006505089e-07</v>
+        <v>7.963526006505031e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.009256620687355e-06</v>
+        <v>1.009256620687095e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>9.317309420391934e-07</v>
+        <v>9.317309420390041e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>9.961435434446796e-07</v>
+        <v>9.961435434444966e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>9.213358064041463e-07</v>
+        <v>9.213358064039022e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.087164453405781e-06</v>
+        <v>1.087164453405605e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.044113900507577e-06</v>
+        <v>1.044113900507401e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.032136546712953e-06</v>
+        <v>1.032136546712938e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>8.386210257408919e-07</v>
+        <v>8.386210257407189e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.580415411265978e-07</v>
+        <v>7.580415411264199e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.757123101750032e-07</v>
+        <v>7.757123101748201e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.958209250282452e-07</v>
+        <v>8.95820925028332e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>9.396774646871423e-07</v>
+        <v>9.396774646869651e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>8.725256132834313e-07</v>
+        <v>8.725256132832467e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>8.783297337938555e-07</v>
+        <v>8.783297337938632e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>8.575399484647015e-07</v>
+        <v>8.57539948464523e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>8.533623198898843e-07</v>
+        <v>8.533623198898319e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>9.838714497954396e-07</v>
+        <v>9.838714497952518e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.967676152361122e-07</v>
+        <v>7.967676152359277e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.400097274942051e-07</v>
+        <v>9.400097274940247e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.058459011954841e-07</v>
+        <v>9.058459011953006e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.882254440323474e-07</v>
+        <v>9.8822544403217e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.579856365108811e-07</v>
+        <v>9.579856365108676e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.047351127236214e-06</v>
+        <v>2.047351127235734e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.153859826188977e-06</v>
+        <v>3.153859826188937e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.510166754920807e-06</v>
+        <v>2.510166754920787e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.198577783102952e-06</v>
+        <v>2.198577783102934e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.286191968481733e-06</v>
+        <v>3.286191968481472e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.062818220295649e-06</v>
+        <v>3.062818220295402e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.065081018910744e-06</v>
+        <v>3.065081018910723e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.279347318980631e-06</v>
+        <v>2.279347318980563e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.492173467516226e-06</v>
+        <v>2.492173467516167e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.438292747573111e-06</v>
+        <v>2.438292747572996e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.844566808074309e-06</v>
+        <v>1.844566808074202e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.568638333805909e-06</v>
+        <v>2.568638333805771e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.76669389241329e-06</v>
+        <v>2.766693892413119e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.072431572653521e-06</v>
+        <v>3.072431572653351e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.932155197205304e-06</v>
+        <v>1.932155197205051e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.105249838573925e-06</v>
+        <v>4.105249838573738e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.028183771681406e-06</v>
+        <v>2.028183771681293e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.079212542132908e-06</v>
+        <v>3.079212542132657e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.138475011204267e-06</v>
+        <v>4.138475011204243e-06</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.996329340923269e-06</v>
+        <v>1.996329340923363e-06</v>
       </c>
       <c r="C2" t="n">
         <v>1.542728103876571e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.244063407700879e-06</v>
+        <v>2.244063407700964e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.31778464255604e-06</v>
+        <v>1.317784642556039e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.549717093154667e-06</v>
+        <v>1.549717093154665e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>3.010421001340206e-06</v>
+        <v>3.010421001340315e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.99673005975e-06</v>
+        <v>1.996730059750329e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.157337470880998e-06</v>
+        <v>2.157337470881093e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.227559607334335e-06</v>
+        <v>2.227559607334536e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.451304493902176e-06</v>
+        <v>2.451304493902268e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>2.117359392722314e-06</v>
+        <v>2.11735939272241e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.449403181213122e-06</v>
+        <v>2.449403181213221e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.694710250223193e-06</v>
+        <v>1.694710250223285e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.550894007423339e-06</v>
+        <v>1.55089400742343e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.518949283805734e-06</v>
+        <v>1.518949283805963e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.857642013924841e-06</v>
+        <v>1.857642013924932e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>2.011484717326115e-06</v>
+        <v>2.011484717326211e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.667750844372391e-06</v>
+        <v>1.667750844372468e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.856728790983169e-06</v>
+        <v>1.856728790983259e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.719696257269037e-06</v>
+        <v>1.719696257269122e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.874529242401759e-06</v>
+        <v>1.874529242401758e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.204201731377381e-06</v>
+        <v>3.204201731377474e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.564021414334726e-06</v>
+        <v>1.564021414334701e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.316207280137524e-06</v>
+        <v>2.316207280137619e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.841364621773601e-06</v>
+        <v>1.841364621773644e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.275125519308166e-06</v>
+        <v>2.275125519308267e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.114423345437295e-06</v>
+        <v>2.114423345437275e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.889657506168137e-06</v>
+        <v>4.889657506168288e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.798672938994044e-06</v>
+        <v>7.798672938994043e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.194688682289579e-06</v>
+        <v>6.194688682289576e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.320923604414868e-06</v>
+        <v>5.320923604414871e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.312283666434425e-06</v>
+        <v>8.312283666434552e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.714405459565172e-06</v>
+        <v>7.714405459565331e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.710256180824386e-06</v>
+        <v>7.710256180824425e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.527015473055111e-06</v>
+        <v>5.527015473055122e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.130894335673633e-06</v>
+        <v>6.130894335673535e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.982869034658771e-06</v>
+        <v>5.982869034658899e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.332552665757521e-06</v>
+        <v>4.332552665757522e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.34098323952618e-06</v>
+        <v>6.340983239526371e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.924946666620622e-06</v>
+        <v>6.924946666620617e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.725024495224293e-06</v>
+        <v>7.725024495224018e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.592368623239771e-06</v>
+        <v>4.592368623239875e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.054330872737407e-05</v>
+        <v>1.054330872737408e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.836999457451149e-06</v>
+        <v>4.836999457451323e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.724467373366882e-06</v>
+        <v>7.724467373366899e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.066655027333529e-05</v>
+        <v>1.066655027333532e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.357228642293539e-06</v>
+        <v>1.357228642293664e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.239054826166518e-06</v>
+        <v>1.23905482616655e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.447524800593688e-06</v>
+        <v>1.447524800593815e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.096989618846956e-06</v>
+        <v>1.096989618846995e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.187857184612538e-06</v>
+        <v>1.187857184612573e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.726853144450064e-06</v>
+        <v>1.726853144450156e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.357374699600404e-06</v>
+        <v>1.357374699600614e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.415914215010216e-06</v>
+        <v>1.415914215010338e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.43773213649043e-06</v>
+        <v>1.437732136490517e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.523061742966379e-06</v>
+        <v>1.523061742966479e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.401342674967669e-06</v>
+        <v>1.401342674967795e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.513337357080526e-06</v>
+        <v>1.513337357080659e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24729202552354e-06</v>
+        <v>1.247292025523666e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.194872693798582e-06</v>
+        <v>1.194872693798704e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.18322921715414e-06</v>
+        <v>1.18322921715402e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.306678740151429e-06</v>
+        <v>1.306678740151551e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.362752599028958e-06</v>
+        <v>1.362752599029086e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.237465638664247e-06</v>
+        <v>1.237465638664363e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.306345881112788e-06</v>
+        <v>1.306345881112916e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.256399131691243e-06</v>
+        <v>1.256399131691355e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.314478644998343e-06</v>
+        <v>1.3144786449984e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.797483945060356e-06</v>
+        <v>1.797483945060481e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.199657479468169e-06</v>
+        <v>1.199657479468067e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.473820394940733e-06</v>
+        <v>1.473820394940851e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.30074582185108e-06</v>
+        <v>1.300745821851195e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.45884657552483e-06</v>
+        <v>1.45884657552494e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.388125952675059e-06</v>
+        <v>1.38812595267505e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.411812783350749e-06</v>
+        <v>2.411812783350794e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.519273257553687e-06</v>
+        <v>3.519273257553727e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.874563873831285e-06</v>
+        <v>2.874563873831323e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.562417674224235e-06</v>
+        <v>2.562417674224272e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65931982826214e-06</v>
+        <v>3.659319828262346e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.437623019831753e-06</v>
+        <v>3.437623019831728e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.430856499383955e-06</v>
+        <v>3.430856499384079e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.644122278045651e-06</v>
+        <v>2.644122278045921e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.864229032366468e-06</v>
+        <v>2.864229032366725e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.810275548347903e-06</v>
+        <v>2.810275548347734e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.208754610876208e-06</v>
+        <v>2.208754610876388e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.940803970832396e-06</v>
+        <v>2.940803970832614e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.1552964911305e-06</v>
+        <v>3.155296491130597e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.44527075630126e-06</v>
+        <v>3.445270756301447e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.303454476465651e-06</v>
+        <v>2.303454476465684e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.472502264955749e-06</v>
+        <v>4.47250226495585e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.392619542935337e-06</v>
+        <v>2.392619542935482e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.445067691926427e-06</v>
+        <v>3.445067691926586e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.505275793749288e-06</v>
+        <v>4.505275793749292e-06</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.007176148559401e-06</v>
+        <v>1.007176148559245e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>8.890023324321334e-07</v>
+        <v>8.890023324321322e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.097472306859554e-06</v>
+        <v>1.097472306859397e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>7.469371251125771e-07</v>
+        <v>7.469371251125769e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.378046908781542e-07</v>
+        <v>8.37804690878155e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.369337859798719e-06</v>
+        <v>1.369337859798857e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.007322205866304e-06</v>
+        <v>1.007322205866196e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.065861721276079e-06</v>
+        <v>1.065861721275921e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.077876506026582e-06</v>
+        <v>1.077876506026567e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.173009249232231e-06</v>
+        <v>1.173009249232062e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051290181233534e-06</v>
+        <v>1.051290181233376e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.163284863346172e-06</v>
+        <v>1.163284863346241e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>8.972395317894045e-07</v>
+        <v>8.972395317892473e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>8.37357409147319e-07</v>
+        <v>8.373574091474053e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>8.25713932502878e-07</v>
+        <v>8.25713932502722e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.566262464172853e-07</v>
+        <v>9.566262464171326e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.012700105294824e-06</v>
+        <v>1.012700105294668e-06</v>
       </c>
       <c r="S6" t="n">
-        <v>8.87413144930108e-07</v>
+        <v>8.874131449299439e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>9.562933873786497e-07</v>
+        <v>9.562933873784983e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>8.988838470399788e-07</v>
+        <v>8.988838470400569e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>9.399071583193789e-07</v>
+        <v>9.399071583193776e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.439968660409097e-06</v>
+        <v>1.439968660409182e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>8.421421948169149e-07</v>
+        <v>8.421421948167688e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.123767901206595e-06</v>
+        <v>1.123767901206432e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.506933281168439e-07</v>
+        <v>9.506933281167774e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.108794081790682e-06</v>
+        <v>1.108794081790522e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03807345894067e-06</v>
+        <v>1.038073458940647e-06</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.061760289616431e-06</v>
+        <v>2.061760289616378e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.169220763819311e-06</v>
+        <v>3.169220763819308e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.524511380096909e-06</v>
+        <v>2.524511380096905e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.212365180489852e-06</v>
+        <v>2.212365180489855e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.301804543610882e-06</v>
+        <v>3.301804543611048e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.077767389367756e-06</v>
+        <v>3.077767389367778e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.080804005649531e-06</v>
+        <v>3.080804005649663e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.294069784311584e-06</v>
+        <v>2.294069784311501e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.506713747715209e-06</v>
+        <v>2.506713747715428e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.452760263696629e-06</v>
+        <v>2.452760263696435e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.858702117141961e-06</v>
+        <v>1.858702117141968e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.583288686181138e-06</v>
+        <v>2.583288686181314e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.780725004451575e-06</v>
+        <v>2.780725004451573e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.087755471649988e-06</v>
+        <v>3.087755471650149e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.945939191814388e-06</v>
+        <v>1.945939191814386e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.122449771221559e-06</v>
+        <v>4.122449771221427e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.042567049200742e-06</v>
+        <v>2.042567049201065e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.095015198192134e-06</v>
+        <v>3.095015198192167e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.155223300014903e-06</v>
+        <v>4.155223300014879e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.370451554754692e-06</v>
+        <v>1.370451554755543e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.191807313945269e-06</v>
+        <v>1.191807313945293e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.509950119986272e-06</v>
+        <v>1.509950119987068e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.851630644997316e-07</v>
+        <v>6.851630645010192e-07</v>
       </c>
       <c r="F2" t="n">
         <v>1.166201846059993e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.530610659224451e-06</v>
+        <v>1.530610659225339e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.237534348060643e-06</v>
+        <v>1.237534348061497e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.255805563787662e-06</v>
+        <v>1.255805563788434e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.356100740451273e-06</v>
+        <v>1.356100740451458e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.394922030836248e-06</v>
+        <v>1.394922030837007e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.278529677662777e-06</v>
+        <v>1.278529677663606e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.358193736113421e-06</v>
+        <v>1.358193736113434e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26283377766561e-06</v>
+        <v>1.262833777666406e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.257417991521963e-06</v>
+        <v>1.257417991522536e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.244784604601611e-06</v>
+        <v>1.24478460460196e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.293931973208878e-06</v>
+        <v>1.293931973209683e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.419843939557453e-06</v>
+        <v>1.419843939556991e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.286357158754492e-06</v>
+        <v>1.286357158755313e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.412605597160663e-06</v>
+        <v>1.412605597161499e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.356864469430777e-06</v>
+        <v>1.356864469431637e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.275427989313361e-06</v>
+        <v>1.275427989313387e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.552128506942951e-06</v>
+        <v>1.55212850694395e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.283466931972765e-06</v>
+        <v>1.283466931973553e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.312093973410487e-06</v>
+        <v>1.312093973411281e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.275968982454097e-06</v>
+        <v>1.275968982454906e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.309875369314548e-06</v>
+        <v>1.309875369315305e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.462090573607871e-06</v>
+        <v>1.462090573607873e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.842071904827925e-06</v>
+        <v>4.842071904829374e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.742272887908483e-06</v>
+        <v>7.742272887908486e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.144633687079654e-06</v>
+        <v>6.144633687081012e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.273744715593959e-06</v>
+        <v>5.273744715593963e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.252269686363195e-06</v>
+        <v>8.252269686363293e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.65763041775905e-06</v>
+        <v>7.657630417759201e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.652441468879716e-06</v>
+        <v>7.652441468879733e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.477115471658449e-06</v>
+        <v>5.477115471659115e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.078801504902242e-06</v>
+        <v>6.078801504902792e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.931313719352553e-06</v>
+        <v>5.931313719353423e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.286990046073275e-06</v>
+        <v>4.286990046073314e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.287993799962619e-06</v>
+        <v>6.287993799962327e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.872408419878243e-06</v>
+        <v>6.872408419878475e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.667142994459836e-06</v>
+        <v>7.667142994461213e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.545862549340569e-06</v>
+        <v>4.545862549341288e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.047496459340125e-05</v>
+        <v>1.047496459340144e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.789605070150054e-06</v>
+        <v>4.789605070149916e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.666587895624783e-06</v>
+        <v>7.666587895625538e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.059903802838709e-05</v>
+        <v>1.059903802838711e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.003939322539324e-06</v>
+        <v>1.003939322540571e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>9.869242958452486e-07</v>
+        <v>9.869242958457852e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.054784911491378e-06</v>
+        <v>1.054784911492704e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>7.427314589005058e-07</v>
+        <v>7.427314589017031e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.241837833089284e-07</v>
+        <v>9.241837833092618e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.062315435435425e-06</v>
+        <v>1.0623154354365e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.554925614919843e-07</v>
+        <v>9.554925614932108e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.621522050730363e-07</v>
+        <v>9.621522050744729e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.000875972114582e-06</v>
+        <v>1.00087597211486e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.01285852372419e-06</v>
+        <v>1.012858523725383e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>9.704348777404871e-07</v>
+        <v>9.70434877741692e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>9.90481271271037e-07</v>
+        <v>9.904812712716293e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>9.647139065021064e-07</v>
+        <v>9.647139065033141e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>9.627399160481062e-07</v>
+        <v>9.627399160492711e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.581351948644178e-07</v>
+        <v>9.581351948656928e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.760488336042179e-07</v>
+        <v>9.76048833605358e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.021942266805265e-06</v>
+        <v>1.021942266806637e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>9.732879026835152e-07</v>
+        <v>9.732879026846565e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.019303975998544e-06</v>
+        <v>1.01930397599976e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>9.989869894863282e-07</v>
+        <v>9.989869894876329e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.007627506542104e-06</v>
+        <v>1.00762750654205e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.070158438253464e-06</v>
+        <v>1.070158438255186e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>9.722344489603577e-07</v>
+        <v>9.722344489616729e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.826686694086776e-07</v>
+        <v>9.826686694101574e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.695015344061308e-07</v>
+        <v>9.695015344075891e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.818600142678738e-07</v>
+        <v>9.818600142692143e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.025905904598058e-06</v>
+        <v>1.025905904598375e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.269304174316698e-06</v>
+        <v>2.269304174318566e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.374492078104603e-06</v>
+        <v>3.37449207810506e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.732644392490063e-06</v>
+        <v>2.732644392491664e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.421334926050454e-06</v>
+        <v>2.421334926050702e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.512281221122236e-06</v>
+        <v>3.512281221123135e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.297709543195883e-06</v>
+        <v>3.297709543197017e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.284660659075877e-06</v>
+        <v>3.284660659076144e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.500770097368394e-06</v>
+        <v>2.500770097369152e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.720077591131667e-06</v>
+        <v>2.720077591132041e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.666320025187822e-06</v>
+        <v>2.666320025188253e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.066983354900927e-06</v>
+        <v>2.066983354901916e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.796325726221217e-06</v>
+        <v>2.796325726222395e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.047661150420668e-06</v>
+        <v>3.047661150420856e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.29900941282795e-06</v>
+        <v>3.299009412828978e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.161339342507462e-06</v>
+        <v>2.161339342509105e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.32242741453627e-06</v>
+        <v>4.322427414536504e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.250180629173326e-06</v>
+        <v>2.250180629174894e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.298807085820897e-06</v>
+        <v>3.298807085821935e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.356215960411142e-06</v>
+        <v>4.356215960411576e-06</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.573978873017469e-07</v>
+        <v>7.57397887302685e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>7.403828606076749e-07</v>
+        <v>7.403828606076659e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>8.082434762538021e-07</v>
+        <v>8.082434762547284e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>4.961900236627067e-07</v>
+        <v>4.961900236637935e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.776423480713015e-07</v>
+        <v>6.776423480712997e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.100190325689372e-07</v>
+        <v>8.100190325698564e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.089511262544102e-07</v>
+        <v>7.089511262552921e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>7.156107698354605e-07</v>
+        <v>7.156107698363723e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.4093999767799e-07</v>
+        <v>7.409399976785442e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>7.663170884866391e-07</v>
+        <v>7.663170884874478e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>7.238934425029286e-07</v>
+        <v>7.238934425038017e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.439398360334408e-07</v>
+        <v>7.439398360334452e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>7.181724712645196e-07</v>
+        <v>7.181724712653948e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.104435131816459e-07</v>
+        <v>7.10443513182588e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.058387919978991e-07</v>
+        <v>7.058387919986981e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.295073983665909e-07</v>
+        <v>7.29507398367492e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>7.754008315676899e-07</v>
+        <v>7.754008315687803e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>7.267464674459294e-07</v>
+        <v>7.267464674468048e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>7.727625407609691e-07</v>
+        <v>7.727625407618648e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>7.466905866198938e-07</v>
+        <v>7.466905866205993e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>7.032213412570885e-07</v>
+        <v>7.032213412569836e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>8.178620353870024e-07</v>
+        <v>8.178620353883186e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.199380460938618e-07</v>
+        <v>7.199380460948144e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.361272341711044e-07</v>
+        <v>7.361272341719937e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.229600991685574e-07</v>
+        <v>7.229600991694517e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.353185790302982e-07</v>
+        <v>7.353185790311999e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.79364469360441e-07</v>
+        <v>7.793644693604425e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.022762739079106e-06</v>
+        <v>2.022762739080478e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.127950642866989e-06</v>
+        <v>3.127950642866979e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.486102957252508e-06</v>
+        <v>2.48610295725346e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.174793490812868e-06</v>
+        <v>2.174793490812871e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.259984818255731e-06</v>
+        <v>3.259984818256394e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.037773568759281e-06</v>
+        <v>3.037773568759757e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.038119223838281e-06</v>
+        <v>3.038119223838285e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.254228662130818e-06</v>
+        <v>2.254228662131272e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.467781188265173e-06</v>
+        <v>2.467781188265385e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.414023622321305e-06</v>
+        <v>2.414023622321349e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82044191966333e-06</v>
+        <v>1.820441919663921e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.544029323354723e-06</v>
+        <v>2.544029323355432e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.743254985135674e-06</v>
+        <v>2.74325498513554e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.046713009961494e-06</v>
+        <v>3.046713009962265e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.909042939640948e-06</v>
+        <v>1.909042939642143e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.075885979298649e-06</v>
+        <v>4.075885979298631e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.0036391939357e-06</v>
+        <v>2.003639193936774e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.052265650583288e-06</v>
+        <v>3.052265650584081e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.109674525173537e-06</v>
+        <v>4.109674525173552e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.693807009055198e-06</v>
+        <v>1.693807009055214e-06</v>
       </c>
       <c r="C2" t="n">
         <v>1.392434690510931e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.061871041058901e-06</v>
+        <v>2.061871041058914e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.531453192079489e-07</v>
+        <v>9.531453192079495e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.399703560877558e-06</v>
+        <v>1.399703560877556e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.534176119658788e-06</v>
+        <v>1.534176119658801e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.458015083587566e-06</v>
+        <v>1.458015083587578e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.969436683274126e-06</v>
+        <v>1.969436683274141e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.576796759477788e-06</v>
+        <v>1.576796759477488e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.710231218803063e-06</v>
+        <v>1.710231218803078e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.657281719356576e-06</v>
+        <v>1.65728171935659e-06</v>
       </c>
       <c r="M2" t="n">
         <v>1.871893541219622e-06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.487586827974761e-06</v>
+        <v>1.487586827974772e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.359746367472288e-06</v>
+        <v>1.359746367472303e-06</v>
       </c>
       <c r="P2" t="n">
-        <v>1.349525129934313e-06</v>
+        <v>1.349525129934327e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.544627239486864e-06</v>
+        <v>1.544627239486878e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.739410849819316e-06</v>
+        <v>1.739410849819329e-06</v>
       </c>
       <c r="S2" t="n">
-        <v>1.580481350719835e-06</v>
+        <v>1.580481350719849e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.727161771417573e-06</v>
+        <v>1.727161771417577e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.565509375457714e-06</v>
+        <v>1.565509375457728e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.568146199674542e-06</v>
+        <v>1.568146199674541e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.797884823526795e-06</v>
+        <v>1.797884823526811e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.442226199417175e-06</v>
+        <v>1.442226199417189e-06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.380121242127341e-06</v>
+        <v>1.380121242127348e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.583335649290196e-06</v>
+        <v>1.58333564929021e-06</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.765741313103304e-06</v>
+        <v>1.765741313103317e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.663508140145493e-06</v>
+        <v>1.663508140145494e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.862688442366734e-06</v>
+        <v>4.862688442366751e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.766993199282268e-06</v>
+        <v>7.766993199282278e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.166498493706684e-06</v>
+        <v>6.166498493706686e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.294648369736109e-06</v>
+        <v>5.294648369736117e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.278225237073988e-06</v>
+        <v>8.278225237074017e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.682333974365916e-06</v>
+        <v>7.682333974365933e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>7.677712735930675e-06</v>
+        <v>7.67771273593069e-06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.49872623480389e-06</v>
+        <v>5.498726234803907e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>6.101354269025778e-06</v>
+        <v>6.101354269025801e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>5.953635576274769e-06</v>
+        <v>5.953635576274799e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.306737546229668e-06</v>
+        <v>4.306737546229692e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>6.310933180883679e-06</v>
+        <v>6.310933180883702e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>6.895461192580313e-06</v>
+        <v>6.89546119258032e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>7.692182469522284e-06</v>
+        <v>7.692182469522316e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.566015340854531e-06</v>
+        <v>4.566015340854548e-06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.050450111141287e-05</v>
+        <v>1.05045011114129e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.810139465496043e-06</v>
+        <v>4.810139465496063e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.691626501631863e-06</v>
+        <v>7.691626501631889e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.062820181829917e-05</v>
+        <v>1.062820181829919e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.153408851454252e-06</v>
+        <v>1.153408851454273e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.091458601594585e-06</v>
+        <v>1.091458601594587e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.287563869093532e-06</v>
+        <v>1.287563869093548e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.714975093187532e-07</v>
+        <v>8.714975093187548e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.04064733704763e-06</v>
+        <v>1.040647337047632e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.095225266749807e-06</v>
+        <v>1.095225266749821e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.067465463429883e-06</v>
+        <v>1.067465463429894e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.253872631100012e-06</v>
+        <v>1.253872631100029e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.11455012557235e-06</v>
+        <v>1.114550125572421e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.159395283044545e-06</v>
+        <v>1.159395283044562e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.140095812260715e-06</v>
+        <v>1.140095812260732e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>1.209476939743806e-06</v>
+        <v>1.209476939743808e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.078244017010061e-06</v>
+        <v>1.078244017010081e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>1.031647670335388e-06</v>
+        <v>1.031647670335406e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.027922149276629e-06</v>
+        <v>1.027922149276646e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.099034577203895e-06</v>
+        <v>1.099034577203912e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.170030915905443e-06</v>
+        <v>1.170030915905458e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.112102979728083e-06</v>
+        <v>1.112102979728099e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.165566270663942e-06</v>
+        <v>1.165566270663954e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.10664587055485e-06</v>
+        <v>1.106645870554867e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.157642148655193e-06</v>
+        <v>1.157642148655679e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.191343992685752e-06</v>
+        <v>1.191343992685769e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.061710600552216e-06</v>
+        <v>1.061710600552232e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.039074072893299e-06</v>
+        <v>1.039074072893308e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.113143338040114e-06</v>
+        <v>1.11314333804013e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.179628060584546e-06</v>
+        <v>1.179628060584563e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.1306165393743e-06</v>
+        <v>1.130616539374302e-06</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.308428923011832e-06</v>
+        <v>2.308428923011843e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>3.414910324196513e-06</v>
+        <v>3.414910324196518e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.771703523139787e-06</v>
+        <v>2.771703523139789e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.460308983125474e-06</v>
+        <v>2.460308983125482e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.553351977424644e-06</v>
+        <v>3.553351977424663e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>3.339946745561508e-06</v>
+        <v>3.339946745561575e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.325629860844975e-06</v>
+        <v>3.32562986084498e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.540257229622337e-06</v>
+        <v>2.540257229622345e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.759908071680562e-06</v>
+        <v>2.759908071680576e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>2.706066342773281e-06</v>
+        <v>2.7060663427733e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.105791349674887e-06</v>
+        <v>2.105791349674905e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>2.836297124052929e-06</v>
+        <v>2.836297124052946e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>3.099385907078385e-06</v>
+        <v>3.099385907078823e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.339746270313668e-06</v>
+        <v>3.339746270313687e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>2.200295061222064e-06</v>
+        <v>2.200295061222085e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.364803391369985e-06</v>
+        <v>4.364803391370007e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.289275438003695e-06</v>
+        <v>2.289275438003715e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.339543626546116e-06</v>
+        <v>3.339543626546132e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.398142116313352e-06</v>
+        <v>4.398142116313363e-06</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.850376789404465e-07</v>
+        <v>8.850376789404605e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.230874290807774e-07</v>
+        <v>8.230874290807753e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.019192696579726e-06</v>
+        <v>1.019192696579736e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.031263368049468e-07</v>
+        <v>6.031263368049462e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.722761645338239e-07</v>
+        <v>7.722761645338229e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>8.199977260854311e-07</v>
+        <v>8.199977260854442e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.990942909160778e-07</v>
+        <v>7.99094290916087e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>9.855014585862054e-07</v>
+        <v>9.855014585862166e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.298833322041462e-07</v>
+        <v>8.298833322042055e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.910241105307384e-07</v>
+        <v>8.910241105307493e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.717246397469083e-07</v>
+        <v>8.717246397469198e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>9.411057672300009e-07</v>
+        <v>9.4110576723e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>8.098728444962556e-07</v>
+        <v>8.098728444962702e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.564201296710144e-07</v>
+        <v>7.564201296710291e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.526946086122548e-07</v>
+        <v>7.526946086122675e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.306634046900891e-07</v>
+        <v>8.306634046900994e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>9.016597433916361e-07</v>
+        <v>9.016597433916467e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>8.437318072142763e-07</v>
+        <v>8.437318072142873e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>8.971950981501356e-07</v>
+        <v>8.971950981501494e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>8.314183298904739e-07</v>
+        <v>8.314183298904899e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>8.181051521158643e-07</v>
+        <v>8.181051521158634e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>9.161164520213778e-07</v>
+        <v>9.161164520213906e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.864830598878403e-07</v>
+        <v>7.864830598878545e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.707029003794926e-07</v>
+        <v>7.707029003795055e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.447721655263079e-07</v>
+        <v>8.447721655263178e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.112568880707401e-07</v>
+        <v>9.112568880707509e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.622453668604951e-07</v>
+        <v>8.622453668604945e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.040057750498025e-06</v>
+        <v>2.040057750498031e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.146539151682706e-06</v>
+        <v>3.146539151682713e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.503332350625982e-06</v>
+        <v>2.503332350625981e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.19193781061167e-06</v>
+        <v>2.191937810611672e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.278124436760272e-06</v>
+        <v>3.278124436760287e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.055279952193338e-06</v>
+        <v>3.055279952193349e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.057258688331169e-06</v>
+        <v>3.057258688331172e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.271886057108531e-06</v>
+        <v>2.271886057108533e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.484680531016184e-06</v>
+        <v>2.484680531016197e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.430838802108909e-06</v>
+        <v>2.430838802108922e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.837420177161083e-06</v>
+        <v>1.837420177161094e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.561069583388555e-06</v>
+        <v>2.561069583388569e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>2.759848910539026e-06</v>
+        <v>2.759848910539031e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>3.064518729649293e-06</v>
+        <v>3.064518729649312e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.925067520557689e-06</v>
+        <v>1.925067520557708e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.09643221885618e-06</v>
+        <v>4.096432218856195e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.020904265489889e-06</v>
+        <v>2.020904265489904e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.071172454032311e-06</v>
+        <v>3.071172454032322e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.12977094379955e-06</v>
+        <v>4.129770943799551e-06</v>
       </c>
     </row>
   </sheetData>
